--- a/Workbook/Most.Traded.Universe.xlsx
+++ b/Workbook/Most.Traded.Universe.xlsx
@@ -44571,7 +44571,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="17">
-        <f>IFERROR(BDP(A3,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C3-AG3,"")</f>
         <v>0</v>
       </c>
       <c r="E3" s="18">
@@ -44607,83 +44607,83 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <f>IFERROR(BDH(A3,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O3">
-        <f>IFERROR(BDH(A3,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P3">
-        <f>IFERROR(BDH(A3,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q3">
-        <f>IFERROR(BDH(A3,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R3">
-        <f>IFERROR(BDH(A3,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S3">
-        <f>IFERROR(BDH(A3,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T3">
-        <f>IFERROR(BDH(A3,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U3">
-        <f>IFERROR(BDH(A3,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V3">
-        <f>IFERROR(BDH(A3,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W3">
-        <f>IFERROR(BDH(A3,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X3">
-        <f>IFERROR(BDH(A3,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y3">
-        <f>IFERROR(BDH(A3,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z3">
-        <f>IFERROR(BDH(A3,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA3">
-        <f>IFERROR(BDH(A3,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB3">
-        <f>IFERROR(BDH(A3,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC3">
-        <f>IFERROR(BDH(A3,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD3">
-        <f>IFERROR(BDH(A3,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE3">
-        <f>IFERROR(BDH(A3,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF3">
-        <f>IFERROR(BDH(A3,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG3">
-        <f>IFERROR(BDH(A3,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -44701,7 +44701,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="22">
-        <f>IFERROR(BDP(A4,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C4-AG4,"")</f>
         <v>0</v>
       </c>
       <c r="E4" s="23">
@@ -44737,83 +44737,83 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <f>IFERROR(BDH(A4,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O4">
-        <f>IFERROR(BDH(A4,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P4">
-        <f>IFERROR(BDH(A4,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q4">
-        <f>IFERROR(BDH(A4,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R4">
-        <f>IFERROR(BDH(A4,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S4">
-        <f>IFERROR(BDH(A4,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T4">
-        <f>IFERROR(BDH(A4,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U4">
-        <f>IFERROR(BDH(A4,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V4">
-        <f>IFERROR(BDH(A4,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W4">
-        <f>IFERROR(BDH(A4,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X4">
-        <f>IFERROR(BDH(A4,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y4">
-        <f>IFERROR(BDH(A4,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z4">
-        <f>IFERROR(BDH(A4,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA4">
-        <f>IFERROR(BDH(A4,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB4">
-        <f>IFERROR(BDH(A4,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC4">
-        <f>IFERROR(BDH(A4,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD4">
-        <f>IFERROR(BDH(A4,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE4">
-        <f>IFERROR(BDH(A4,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF4">
-        <f>IFERROR(BDH(A4,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG4">
-        <f>IFERROR(BDH(A4,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -44831,7 +44831,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="17">
-        <f>IFERROR(BDP(A5,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C5-AG5,"")</f>
         <v>0</v>
       </c>
       <c r="E5" s="18">
@@ -44867,83 +44867,83 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <f>IFERROR(BDH(A5,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O5">
-        <f>IFERROR(BDH(A5,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P5">
-        <f>IFERROR(BDH(A5,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q5">
-        <f>IFERROR(BDH(A5,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R5">
-        <f>IFERROR(BDH(A5,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S5">
-        <f>IFERROR(BDH(A5,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T5">
-        <f>IFERROR(BDH(A5,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U5">
-        <f>IFERROR(BDH(A5,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V5">
-        <f>IFERROR(BDH(A5,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W5">
-        <f>IFERROR(BDH(A5,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X5">
-        <f>IFERROR(BDH(A5,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y5">
-        <f>IFERROR(BDH(A5,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z5">
-        <f>IFERROR(BDH(A5,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA5">
-        <f>IFERROR(BDH(A5,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB5">
-        <f>IFERROR(BDH(A5,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC5">
-        <f>IFERROR(BDH(A5,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD5">
-        <f>IFERROR(BDH(A5,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE5">
-        <f>IFERROR(BDH(A5,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF5">
-        <f>IFERROR(BDH(A5,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG5">
-        <f>IFERROR(BDH(A5,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -44961,7 +44961,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="22">
-        <f>IFERROR(BDP(A6,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C6-AG6,"")</f>
         <v>0</v>
       </c>
       <c r="E6" s="23">
@@ -44997,83 +44997,83 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <f>IFERROR(BDH(A6,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O6">
-        <f>IFERROR(BDH(A6,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P6">
-        <f>IFERROR(BDH(A6,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q6">
-        <f>IFERROR(BDH(A6,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R6">
-        <f>IFERROR(BDH(A6,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S6">
-        <f>IFERROR(BDH(A6,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T6">
-        <f>IFERROR(BDH(A6,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U6">
-        <f>IFERROR(BDH(A6,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V6">
-        <f>IFERROR(BDH(A6,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W6">
-        <f>IFERROR(BDH(A6,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X6">
-        <f>IFERROR(BDH(A6,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y6">
-        <f>IFERROR(BDH(A6,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z6">
-        <f>IFERROR(BDH(A6,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA6">
-        <f>IFERROR(BDH(A6,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB6">
-        <f>IFERROR(BDH(A6,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC6">
-        <f>IFERROR(BDH(A6,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD6">
-        <f>IFERROR(BDH(A6,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE6">
-        <f>IFERROR(BDH(A6,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF6">
-        <f>IFERROR(BDH(A6,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG6">
-        <f>IFERROR(BDH(A6,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -45091,7 +45091,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="17">
-        <f>IFERROR(BDP(A7,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C7-AG7,"")</f>
         <v>0</v>
       </c>
       <c r="E7" s="18">
@@ -45127,83 +45127,83 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <f>IFERROR(BDH(A7,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O7">
-        <f>IFERROR(BDH(A7,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P7">
-        <f>IFERROR(BDH(A7,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q7">
-        <f>IFERROR(BDH(A7,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R7">
-        <f>IFERROR(BDH(A7,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S7">
-        <f>IFERROR(BDH(A7,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T7">
-        <f>IFERROR(BDH(A7,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U7">
-        <f>IFERROR(BDH(A7,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V7">
-        <f>IFERROR(BDH(A7,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W7">
-        <f>IFERROR(BDH(A7,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X7">
-        <f>IFERROR(BDH(A7,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y7">
-        <f>IFERROR(BDH(A7,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z7">
-        <f>IFERROR(BDH(A7,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA7">
-        <f>IFERROR(BDH(A7,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB7">
-        <f>IFERROR(BDH(A7,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC7">
-        <f>IFERROR(BDH(A7,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD7">
-        <f>IFERROR(BDH(A7,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE7">
-        <f>IFERROR(BDH(A7,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF7">
-        <f>IFERROR(BDH(A7,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG7">
-        <f>IFERROR(BDH(A7,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -45221,7 +45221,7 @@
         <v>0</v>
       </c>
       <c r="D8" s="22">
-        <f>IFERROR(BDP(A8,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C8-AG8,"")</f>
         <v>0</v>
       </c>
       <c r="E8" s="23">
@@ -45257,83 +45257,83 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <f>IFERROR(BDH(A8,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O8">
-        <f>IFERROR(BDH(A8,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P8">
-        <f>IFERROR(BDH(A8,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q8">
-        <f>IFERROR(BDH(A8,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R8">
-        <f>IFERROR(BDH(A8,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S8">
-        <f>IFERROR(BDH(A8,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T8">
-        <f>IFERROR(BDH(A8,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U8">
-        <f>IFERROR(BDH(A8,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V8">
-        <f>IFERROR(BDH(A8,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W8">
-        <f>IFERROR(BDH(A8,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X8">
-        <f>IFERROR(BDH(A8,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y8">
-        <f>IFERROR(BDH(A8,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z8">
-        <f>IFERROR(BDH(A8,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA8">
-        <f>IFERROR(BDH(A8,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB8">
-        <f>IFERROR(BDH(A8,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC8">
-        <f>IFERROR(BDH(A8,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD8">
-        <f>IFERROR(BDH(A8,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE8">
-        <f>IFERROR(BDH(A8,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF8">
-        <f>IFERROR(BDH(A8,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG8">
-        <f>IFERROR(BDH(A8,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -45351,7 +45351,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="17">
-        <f>IFERROR(BDP(A9,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C9-AG9,"")</f>
         <v>0</v>
       </c>
       <c r="E9" s="18">
@@ -45387,83 +45387,83 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <f>IFERROR(BDH(A9,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O9">
-        <f>IFERROR(BDH(A9,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P9">
-        <f>IFERROR(BDH(A9,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q9">
-        <f>IFERROR(BDH(A9,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R9">
-        <f>IFERROR(BDH(A9,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S9">
-        <f>IFERROR(BDH(A9,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T9">
-        <f>IFERROR(BDH(A9,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U9">
-        <f>IFERROR(BDH(A9,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V9">
-        <f>IFERROR(BDH(A9,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W9">
-        <f>IFERROR(BDH(A9,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X9">
-        <f>IFERROR(BDH(A9,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y9">
-        <f>IFERROR(BDH(A9,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z9">
-        <f>IFERROR(BDH(A9,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA9">
-        <f>IFERROR(BDH(A9,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB9">
-        <f>IFERROR(BDH(A9,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC9">
-        <f>IFERROR(BDH(A9,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD9">
-        <f>IFERROR(BDH(A9,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE9">
-        <f>IFERROR(BDH(A9,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF9">
-        <f>IFERROR(BDH(A9,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG9">
-        <f>IFERROR(BDH(A9,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -45481,7 +45481,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="22">
-        <f>IFERROR(BDP(A10,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C10-AG10,"")</f>
         <v>0</v>
       </c>
       <c r="E10" s="23">
@@ -45517,83 +45517,83 @@
         <v>0</v>
       </c>
       <c r="N10">
-        <f>IFERROR(BDH(A10,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O10">
-        <f>IFERROR(BDH(A10,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P10">
-        <f>IFERROR(BDH(A10,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q10">
-        <f>IFERROR(BDH(A10,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R10">
-        <f>IFERROR(BDH(A10,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S10">
-        <f>IFERROR(BDH(A10,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T10">
-        <f>IFERROR(BDH(A10,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U10">
-        <f>IFERROR(BDH(A10,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V10">
-        <f>IFERROR(BDH(A10,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W10">
-        <f>IFERROR(BDH(A10,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X10">
-        <f>IFERROR(BDH(A10,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y10">
-        <f>IFERROR(BDH(A10,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z10">
-        <f>IFERROR(BDH(A10,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA10">
-        <f>IFERROR(BDH(A10,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB10">
-        <f>IFERROR(BDH(A10,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC10">
-        <f>IFERROR(BDH(A10,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD10">
-        <f>IFERROR(BDH(A10,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE10">
-        <f>IFERROR(BDH(A10,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF10">
-        <f>IFERROR(BDH(A10,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG10">
-        <f>IFERROR(BDH(A10,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -45611,7 +45611,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="17">
-        <f>IFERROR(BDP(A11,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C11-AG11,"")</f>
         <v>0</v>
       </c>
       <c r="E11" s="18">
@@ -45647,83 +45647,83 @@
         <v>0</v>
       </c>
       <c r="N11">
-        <f>IFERROR(BDH(A11,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O11">
-        <f>IFERROR(BDH(A11,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P11">
-        <f>IFERROR(BDH(A11,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q11">
-        <f>IFERROR(BDH(A11,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R11">
-        <f>IFERROR(BDH(A11,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S11">
-        <f>IFERROR(BDH(A11,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T11">
-        <f>IFERROR(BDH(A11,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U11">
-        <f>IFERROR(BDH(A11,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V11">
-        <f>IFERROR(BDH(A11,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W11">
-        <f>IFERROR(BDH(A11,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X11">
-        <f>IFERROR(BDH(A11,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y11">
-        <f>IFERROR(BDH(A11,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z11">
-        <f>IFERROR(BDH(A11,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA11">
-        <f>IFERROR(BDH(A11,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB11">
-        <f>IFERROR(BDH(A11,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC11">
-        <f>IFERROR(BDH(A11,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD11">
-        <f>IFERROR(BDH(A11,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE11">
-        <f>IFERROR(BDH(A11,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF11">
-        <f>IFERROR(BDH(A11,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG11">
-        <f>IFERROR(BDH(A11,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -45741,7 +45741,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="22">
-        <f>IFERROR(BDP(A12,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C12-AG12,"")</f>
         <v>0</v>
       </c>
       <c r="E12" s="23">
@@ -45777,83 +45777,83 @@
         <v>0</v>
       </c>
       <c r="N12">
-        <f>IFERROR(BDH(A12,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O12">
-        <f>IFERROR(BDH(A12,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P12">
-        <f>IFERROR(BDH(A12,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q12">
-        <f>IFERROR(BDH(A12,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R12">
-        <f>IFERROR(BDH(A12,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S12">
-        <f>IFERROR(BDH(A12,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T12">
-        <f>IFERROR(BDH(A12,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U12">
-        <f>IFERROR(BDH(A12,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V12">
-        <f>IFERROR(BDH(A12,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W12">
-        <f>IFERROR(BDH(A12,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X12">
-        <f>IFERROR(BDH(A12,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y12">
-        <f>IFERROR(BDH(A12,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z12">
-        <f>IFERROR(BDH(A12,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA12">
-        <f>IFERROR(BDH(A12,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB12">
-        <f>IFERROR(BDH(A12,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC12">
-        <f>IFERROR(BDH(A12,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD12">
-        <f>IFERROR(BDH(A12,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE12">
-        <f>IFERROR(BDH(A12,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF12">
-        <f>IFERROR(BDH(A12,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG12">
-        <f>IFERROR(BDH(A12,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -45871,7 +45871,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="17">
-        <f>IFERROR(BDP(A13,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C13-AG13,"")</f>
         <v>0</v>
       </c>
       <c r="E13" s="18">
@@ -45907,83 +45907,83 @@
         <v>0</v>
       </c>
       <c r="N13">
-        <f>IFERROR(BDH(A13,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O13">
-        <f>IFERROR(BDH(A13,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P13">
-        <f>IFERROR(BDH(A13,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q13">
-        <f>IFERROR(BDH(A13,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R13">
-        <f>IFERROR(BDH(A13,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S13">
-        <f>IFERROR(BDH(A13,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T13">
-        <f>IFERROR(BDH(A13,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U13">
-        <f>IFERROR(BDH(A13,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V13">
-        <f>IFERROR(BDH(A13,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W13">
-        <f>IFERROR(BDH(A13,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X13">
-        <f>IFERROR(BDH(A13,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y13">
-        <f>IFERROR(BDH(A13,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z13">
-        <f>IFERROR(BDH(A13,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA13">
-        <f>IFERROR(BDH(A13,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB13">
-        <f>IFERROR(BDH(A13,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC13">
-        <f>IFERROR(BDH(A13,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD13">
-        <f>IFERROR(BDH(A13,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE13">
-        <f>IFERROR(BDH(A13,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF13">
-        <f>IFERROR(BDH(A13,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG13">
-        <f>IFERROR(BDH(A13,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -46001,7 +46001,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="22">
-        <f>IFERROR(BDP(A14,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C14-AG14,"")</f>
         <v>0</v>
       </c>
       <c r="E14" s="23">
@@ -46037,83 +46037,83 @@
         <v>0</v>
       </c>
       <c r="N14">
-        <f>IFERROR(BDH(A14,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O14">
-        <f>IFERROR(BDH(A14,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P14">
-        <f>IFERROR(BDH(A14,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q14">
-        <f>IFERROR(BDH(A14,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R14">
-        <f>IFERROR(BDH(A14,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S14">
-        <f>IFERROR(BDH(A14,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T14">
-        <f>IFERROR(BDH(A14,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U14">
-        <f>IFERROR(BDH(A14,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V14">
-        <f>IFERROR(BDH(A14,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W14">
-        <f>IFERROR(BDH(A14,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X14">
-        <f>IFERROR(BDH(A14,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y14">
-        <f>IFERROR(BDH(A14,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z14">
-        <f>IFERROR(BDH(A14,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA14">
-        <f>IFERROR(BDH(A14,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB14">
-        <f>IFERROR(BDH(A14,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC14">
-        <f>IFERROR(BDH(A14,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD14">
-        <f>IFERROR(BDH(A14,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE14">
-        <f>IFERROR(BDH(A14,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF14">
-        <f>IFERROR(BDH(A14,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG14">
-        <f>IFERROR(BDH(A14,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -46131,7 +46131,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="17">
-        <f>IFERROR(BDP(A15,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C15-AG15,"")</f>
         <v>0</v>
       </c>
       <c r="E15" s="18">
@@ -46167,83 +46167,83 @@
         <v>0</v>
       </c>
       <c r="N15">
-        <f>IFERROR(BDH(A15,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O15">
-        <f>IFERROR(BDH(A15,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P15">
-        <f>IFERROR(BDH(A15,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q15">
-        <f>IFERROR(BDH(A15,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R15">
-        <f>IFERROR(BDH(A15,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S15">
-        <f>IFERROR(BDH(A15,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T15">
-        <f>IFERROR(BDH(A15,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U15">
-        <f>IFERROR(BDH(A15,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V15">
-        <f>IFERROR(BDH(A15,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W15">
-        <f>IFERROR(BDH(A15,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X15">
-        <f>IFERROR(BDH(A15,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y15">
-        <f>IFERROR(BDH(A15,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z15">
-        <f>IFERROR(BDH(A15,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA15">
-        <f>IFERROR(BDH(A15,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB15">
-        <f>IFERROR(BDH(A15,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC15">
-        <f>IFERROR(BDH(A15,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD15">
-        <f>IFERROR(BDH(A15,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE15">
-        <f>IFERROR(BDH(A15,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF15">
-        <f>IFERROR(BDH(A15,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG15">
-        <f>IFERROR(BDH(A15,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -46261,7 +46261,7 @@
         <v>0</v>
       </c>
       <c r="D16" s="22">
-        <f>IFERROR(BDP(A16,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C16-AG16,"")</f>
         <v>0</v>
       </c>
       <c r="E16" s="23">
@@ -46297,83 +46297,83 @@
         <v>0</v>
       </c>
       <c r="N16">
-        <f>IFERROR(BDH(A16,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O16">
-        <f>IFERROR(BDH(A16,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P16">
-        <f>IFERROR(BDH(A16,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q16">
-        <f>IFERROR(BDH(A16,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R16">
-        <f>IFERROR(BDH(A16,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S16">
-        <f>IFERROR(BDH(A16,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T16">
-        <f>IFERROR(BDH(A16,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U16">
-        <f>IFERROR(BDH(A16,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V16">
-        <f>IFERROR(BDH(A16,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W16">
-        <f>IFERROR(BDH(A16,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X16">
-        <f>IFERROR(BDH(A16,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y16">
-        <f>IFERROR(BDH(A16,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z16">
-        <f>IFERROR(BDH(A16,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA16">
-        <f>IFERROR(BDH(A16,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB16">
-        <f>IFERROR(BDH(A16,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC16">
-        <f>IFERROR(BDH(A16,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD16">
-        <f>IFERROR(BDH(A16,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE16">
-        <f>IFERROR(BDH(A16,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF16">
-        <f>IFERROR(BDH(A16,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG16">
-        <f>IFERROR(BDH(A16,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -46391,7 +46391,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="17">
-        <f>IFERROR(BDP(A17,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C17-AG17,"")</f>
         <v>0</v>
       </c>
       <c r="E17" s="18">
@@ -46427,83 +46427,83 @@
         <v>0</v>
       </c>
       <c r="N17">
-        <f>IFERROR(BDH(A17,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O17">
-        <f>IFERROR(BDH(A17,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P17">
-        <f>IFERROR(BDH(A17,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q17">
-        <f>IFERROR(BDH(A17,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R17">
-        <f>IFERROR(BDH(A17,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S17">
-        <f>IFERROR(BDH(A17,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T17">
-        <f>IFERROR(BDH(A17,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U17">
-        <f>IFERROR(BDH(A17,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V17">
-        <f>IFERROR(BDH(A17,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W17">
-        <f>IFERROR(BDH(A17,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X17">
-        <f>IFERROR(BDH(A17,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y17">
-        <f>IFERROR(BDH(A17,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z17">
-        <f>IFERROR(BDH(A17,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA17">
-        <f>IFERROR(BDH(A17,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB17">
-        <f>IFERROR(BDH(A17,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC17">
-        <f>IFERROR(BDH(A17,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD17">
-        <f>IFERROR(BDH(A17,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE17">
-        <f>IFERROR(BDH(A17,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF17">
-        <f>IFERROR(BDH(A17,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG17">
-        <f>IFERROR(BDH(A17,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -55994,7 +55994,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="17">
-        <f>IFERROR(BDP(A3,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C3-AG3,"")</f>
         <v>0</v>
       </c>
       <c r="E3" s="18">
@@ -56030,83 +56030,83 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <f>IFERROR(BDH(A3,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O3">
-        <f>IFERROR(BDH(A3,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P3">
-        <f>IFERROR(BDH(A3,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q3">
-        <f>IFERROR(BDH(A3,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R3">
-        <f>IFERROR(BDH(A3,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S3">
-        <f>IFERROR(BDH(A3,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T3">
-        <f>IFERROR(BDH(A3,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U3">
-        <f>IFERROR(BDH(A3,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V3">
-        <f>IFERROR(BDH(A3,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W3">
-        <f>IFERROR(BDH(A3,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X3">
-        <f>IFERROR(BDH(A3,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y3">
-        <f>IFERROR(BDH(A3,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z3">
-        <f>IFERROR(BDH(A3,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA3">
-        <f>IFERROR(BDH(A3,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB3">
-        <f>IFERROR(BDH(A3,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC3">
-        <f>IFERROR(BDH(A3,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD3">
-        <f>IFERROR(BDH(A3,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE3">
-        <f>IFERROR(BDH(A3,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF3">
-        <f>IFERROR(BDH(A3,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG3">
-        <f>IFERROR(BDH(A3,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -56124,7 +56124,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="22">
-        <f>IFERROR(BDP(A4,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C4-AG4,"")</f>
         <v>0</v>
       </c>
       <c r="E4" s="23">
@@ -56160,83 +56160,83 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <f>IFERROR(BDH(A4,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O4">
-        <f>IFERROR(BDH(A4,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P4">
-        <f>IFERROR(BDH(A4,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q4">
-        <f>IFERROR(BDH(A4,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R4">
-        <f>IFERROR(BDH(A4,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S4">
-        <f>IFERROR(BDH(A4,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T4">
-        <f>IFERROR(BDH(A4,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U4">
-        <f>IFERROR(BDH(A4,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V4">
-        <f>IFERROR(BDH(A4,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W4">
-        <f>IFERROR(BDH(A4,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X4">
-        <f>IFERROR(BDH(A4,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y4">
-        <f>IFERROR(BDH(A4,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z4">
-        <f>IFERROR(BDH(A4,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA4">
-        <f>IFERROR(BDH(A4,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB4">
-        <f>IFERROR(BDH(A4,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC4">
-        <f>IFERROR(BDH(A4,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD4">
-        <f>IFERROR(BDH(A4,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE4">
-        <f>IFERROR(BDH(A4,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF4">
-        <f>IFERROR(BDH(A4,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG4">
-        <f>IFERROR(BDH(A4,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -56254,7 +56254,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="17">
-        <f>IFERROR(BDP(A5,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C5-AG5,"")</f>
         <v>0</v>
       </c>
       <c r="E5" s="18">
@@ -56290,83 +56290,83 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <f>IFERROR(BDH(A5,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O5">
-        <f>IFERROR(BDH(A5,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P5">
-        <f>IFERROR(BDH(A5,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q5">
-        <f>IFERROR(BDH(A5,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R5">
-        <f>IFERROR(BDH(A5,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S5">
-        <f>IFERROR(BDH(A5,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T5">
-        <f>IFERROR(BDH(A5,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U5">
-        <f>IFERROR(BDH(A5,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V5">
-        <f>IFERROR(BDH(A5,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W5">
-        <f>IFERROR(BDH(A5,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X5">
-        <f>IFERROR(BDH(A5,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y5">
-        <f>IFERROR(BDH(A5,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z5">
-        <f>IFERROR(BDH(A5,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA5">
-        <f>IFERROR(BDH(A5,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB5">
-        <f>IFERROR(BDH(A5,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC5">
-        <f>IFERROR(BDH(A5,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD5">
-        <f>IFERROR(BDH(A5,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE5">
-        <f>IFERROR(BDH(A5,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF5">
-        <f>IFERROR(BDH(A5,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG5">
-        <f>IFERROR(BDH(A5,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -56384,7 +56384,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="22">
-        <f>IFERROR(BDP(A6,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C6-AG6,"")</f>
         <v>0</v>
       </c>
       <c r="E6" s="23">
@@ -56420,83 +56420,83 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <f>IFERROR(BDH(A6,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O6">
-        <f>IFERROR(BDH(A6,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P6">
-        <f>IFERROR(BDH(A6,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q6">
-        <f>IFERROR(BDH(A6,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R6">
-        <f>IFERROR(BDH(A6,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S6">
-        <f>IFERROR(BDH(A6,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T6">
-        <f>IFERROR(BDH(A6,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U6">
-        <f>IFERROR(BDH(A6,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V6">
-        <f>IFERROR(BDH(A6,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W6">
-        <f>IFERROR(BDH(A6,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X6">
-        <f>IFERROR(BDH(A6,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y6">
-        <f>IFERROR(BDH(A6,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z6">
-        <f>IFERROR(BDH(A6,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA6">
-        <f>IFERROR(BDH(A6,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB6">
-        <f>IFERROR(BDH(A6,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC6">
-        <f>IFERROR(BDH(A6,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD6">
-        <f>IFERROR(BDH(A6,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE6">
-        <f>IFERROR(BDH(A6,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF6">
-        <f>IFERROR(BDH(A6,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG6">
-        <f>IFERROR(BDH(A6,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -56514,7 +56514,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="17">
-        <f>IFERROR(BDP(A7,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C7-AG7,"")</f>
         <v>0</v>
       </c>
       <c r="E7" s="18">
@@ -56550,83 +56550,83 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <f>IFERROR(BDH(A7,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O7">
-        <f>IFERROR(BDH(A7,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P7">
-        <f>IFERROR(BDH(A7,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q7">
-        <f>IFERROR(BDH(A7,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R7">
-        <f>IFERROR(BDH(A7,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S7">
-        <f>IFERROR(BDH(A7,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T7">
-        <f>IFERROR(BDH(A7,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U7">
-        <f>IFERROR(BDH(A7,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V7">
-        <f>IFERROR(BDH(A7,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W7">
-        <f>IFERROR(BDH(A7,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X7">
-        <f>IFERROR(BDH(A7,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y7">
-        <f>IFERROR(BDH(A7,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z7">
-        <f>IFERROR(BDH(A7,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA7">
-        <f>IFERROR(BDH(A7,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB7">
-        <f>IFERROR(BDH(A7,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC7">
-        <f>IFERROR(BDH(A7,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD7">
-        <f>IFERROR(BDH(A7,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE7">
-        <f>IFERROR(BDH(A7,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF7">
-        <f>IFERROR(BDH(A7,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG7">
-        <f>IFERROR(BDH(A7,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -56644,7 +56644,7 @@
         <v>0</v>
       </c>
       <c r="D8" s="22">
-        <f>IFERROR(BDP(A8,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C8-AG8,"")</f>
         <v>0</v>
       </c>
       <c r="E8" s="23">
@@ -56680,83 +56680,83 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <f>IFERROR(BDH(A8,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O8">
-        <f>IFERROR(BDH(A8,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P8">
-        <f>IFERROR(BDH(A8,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q8">
-        <f>IFERROR(BDH(A8,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R8">
-        <f>IFERROR(BDH(A8,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S8">
-        <f>IFERROR(BDH(A8,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T8">
-        <f>IFERROR(BDH(A8,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U8">
-        <f>IFERROR(BDH(A8,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V8">
-        <f>IFERROR(BDH(A8,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W8">
-        <f>IFERROR(BDH(A8,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X8">
-        <f>IFERROR(BDH(A8,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y8">
-        <f>IFERROR(BDH(A8,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z8">
-        <f>IFERROR(BDH(A8,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA8">
-        <f>IFERROR(BDH(A8,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB8">
-        <f>IFERROR(BDH(A8,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC8">
-        <f>IFERROR(BDH(A8,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD8">
-        <f>IFERROR(BDH(A8,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE8">
-        <f>IFERROR(BDH(A8,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF8">
-        <f>IFERROR(BDH(A8,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG8">
-        <f>IFERROR(BDH(A8,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -56774,7 +56774,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="17">
-        <f>IFERROR(BDP(A9,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C9-AG9,"")</f>
         <v>0</v>
       </c>
       <c r="E9" s="18">
@@ -56810,83 +56810,83 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <f>IFERROR(BDH(A9,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O9">
-        <f>IFERROR(BDH(A9,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P9">
-        <f>IFERROR(BDH(A9,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q9">
-        <f>IFERROR(BDH(A9,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R9">
-        <f>IFERROR(BDH(A9,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S9">
-        <f>IFERROR(BDH(A9,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T9">
-        <f>IFERROR(BDH(A9,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U9">
-        <f>IFERROR(BDH(A9,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V9">
-        <f>IFERROR(BDH(A9,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W9">
-        <f>IFERROR(BDH(A9,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X9">
-        <f>IFERROR(BDH(A9,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y9">
-        <f>IFERROR(BDH(A9,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z9">
-        <f>IFERROR(BDH(A9,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA9">
-        <f>IFERROR(BDH(A9,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB9">
-        <f>IFERROR(BDH(A9,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC9">
-        <f>IFERROR(BDH(A9,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD9">
-        <f>IFERROR(BDH(A9,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE9">
-        <f>IFERROR(BDH(A9,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF9">
-        <f>IFERROR(BDH(A9,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG9">
-        <f>IFERROR(BDH(A9,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -56904,7 +56904,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="22">
-        <f>IFERROR(BDP(A10,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C10-AG10,"")</f>
         <v>0</v>
       </c>
       <c r="E10" s="23">
@@ -56940,83 +56940,83 @@
         <v>0</v>
       </c>
       <c r="N10">
-        <f>IFERROR(BDH(A10,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O10">
-        <f>IFERROR(BDH(A10,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P10">
-        <f>IFERROR(BDH(A10,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q10">
-        <f>IFERROR(BDH(A10,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R10">
-        <f>IFERROR(BDH(A10,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S10">
-        <f>IFERROR(BDH(A10,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T10">
-        <f>IFERROR(BDH(A10,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U10">
-        <f>IFERROR(BDH(A10,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V10">
-        <f>IFERROR(BDH(A10,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W10">
-        <f>IFERROR(BDH(A10,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X10">
-        <f>IFERROR(BDH(A10,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y10">
-        <f>IFERROR(BDH(A10,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z10">
-        <f>IFERROR(BDH(A10,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA10">
-        <f>IFERROR(BDH(A10,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB10">
-        <f>IFERROR(BDH(A10,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC10">
-        <f>IFERROR(BDH(A10,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD10">
-        <f>IFERROR(BDH(A10,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE10">
-        <f>IFERROR(BDH(A10,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF10">
-        <f>IFERROR(BDH(A10,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG10">
-        <f>IFERROR(BDH(A10,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -57034,7 +57034,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="17">
-        <f>IFERROR(BDP(A11,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C11-AG11,"")</f>
         <v>0</v>
       </c>
       <c r="E11" s="18">
@@ -57070,83 +57070,83 @@
         <v>0</v>
       </c>
       <c r="N11">
-        <f>IFERROR(BDH(A11,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O11">
-        <f>IFERROR(BDH(A11,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P11">
-        <f>IFERROR(BDH(A11,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q11">
-        <f>IFERROR(BDH(A11,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R11">
-        <f>IFERROR(BDH(A11,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S11">
-        <f>IFERROR(BDH(A11,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T11">
-        <f>IFERROR(BDH(A11,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U11">
-        <f>IFERROR(BDH(A11,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V11">
-        <f>IFERROR(BDH(A11,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W11">
-        <f>IFERROR(BDH(A11,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X11">
-        <f>IFERROR(BDH(A11,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y11">
-        <f>IFERROR(BDH(A11,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z11">
-        <f>IFERROR(BDH(A11,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA11">
-        <f>IFERROR(BDH(A11,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB11">
-        <f>IFERROR(BDH(A11,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC11">
-        <f>IFERROR(BDH(A11,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD11">
-        <f>IFERROR(BDH(A11,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE11">
-        <f>IFERROR(BDH(A11,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF11">
-        <f>IFERROR(BDH(A11,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG11">
-        <f>IFERROR(BDH(A11,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -57164,7 +57164,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="22">
-        <f>IFERROR(BDP(A12,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C12-AG12,"")</f>
         <v>0</v>
       </c>
       <c r="E12" s="23">
@@ -57200,83 +57200,83 @@
         <v>0</v>
       </c>
       <c r="N12">
-        <f>IFERROR(BDH(A12,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O12">
-        <f>IFERROR(BDH(A12,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P12">
-        <f>IFERROR(BDH(A12,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q12">
-        <f>IFERROR(BDH(A12,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R12">
-        <f>IFERROR(BDH(A12,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S12">
-        <f>IFERROR(BDH(A12,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T12">
-        <f>IFERROR(BDH(A12,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U12">
-        <f>IFERROR(BDH(A12,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V12">
-        <f>IFERROR(BDH(A12,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W12">
-        <f>IFERROR(BDH(A12,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X12">
-        <f>IFERROR(BDH(A12,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y12">
-        <f>IFERROR(BDH(A12,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z12">
-        <f>IFERROR(BDH(A12,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA12">
-        <f>IFERROR(BDH(A12,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB12">
-        <f>IFERROR(BDH(A12,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC12">
-        <f>IFERROR(BDH(A12,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD12">
-        <f>IFERROR(BDH(A12,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE12">
-        <f>IFERROR(BDH(A12,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF12">
-        <f>IFERROR(BDH(A12,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG12">
-        <f>IFERROR(BDH(A12,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -57294,7 +57294,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="17">
-        <f>IFERROR(BDP(A13,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C13-AG13,"")</f>
         <v>0</v>
       </c>
       <c r="E13" s="18">
@@ -57330,83 +57330,83 @@
         <v>0</v>
       </c>
       <c r="N13">
-        <f>IFERROR(BDH(A13,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O13">
-        <f>IFERROR(BDH(A13,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P13">
-        <f>IFERROR(BDH(A13,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q13">
-        <f>IFERROR(BDH(A13,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R13">
-        <f>IFERROR(BDH(A13,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S13">
-        <f>IFERROR(BDH(A13,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T13">
-        <f>IFERROR(BDH(A13,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U13">
-        <f>IFERROR(BDH(A13,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V13">
-        <f>IFERROR(BDH(A13,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W13">
-        <f>IFERROR(BDH(A13,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X13">
-        <f>IFERROR(BDH(A13,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y13">
-        <f>IFERROR(BDH(A13,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z13">
-        <f>IFERROR(BDH(A13,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA13">
-        <f>IFERROR(BDH(A13,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB13">
-        <f>IFERROR(BDH(A13,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC13">
-        <f>IFERROR(BDH(A13,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD13">
-        <f>IFERROR(BDH(A13,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE13">
-        <f>IFERROR(BDH(A13,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF13">
-        <f>IFERROR(BDH(A13,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG13">
-        <f>IFERROR(BDH(A13,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -57424,7 +57424,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="22">
-        <f>IFERROR(BDP(A14,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C14-AG14,"")</f>
         <v>0</v>
       </c>
       <c r="E14" s="23">
@@ -57460,83 +57460,83 @@
         <v>0</v>
       </c>
       <c r="N14">
-        <f>IFERROR(BDH(A14,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O14">
-        <f>IFERROR(BDH(A14,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P14">
-        <f>IFERROR(BDH(A14,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q14">
-        <f>IFERROR(BDH(A14,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R14">
-        <f>IFERROR(BDH(A14,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S14">
-        <f>IFERROR(BDH(A14,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T14">
-        <f>IFERROR(BDH(A14,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U14">
-        <f>IFERROR(BDH(A14,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V14">
-        <f>IFERROR(BDH(A14,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W14">
-        <f>IFERROR(BDH(A14,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X14">
-        <f>IFERROR(BDH(A14,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y14">
-        <f>IFERROR(BDH(A14,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z14">
-        <f>IFERROR(BDH(A14,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA14">
-        <f>IFERROR(BDH(A14,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB14">
-        <f>IFERROR(BDH(A14,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC14">
-        <f>IFERROR(BDH(A14,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD14">
-        <f>IFERROR(BDH(A14,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE14">
-        <f>IFERROR(BDH(A14,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF14">
-        <f>IFERROR(BDH(A14,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG14">
-        <f>IFERROR(BDH(A14,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -57554,7 +57554,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="17">
-        <f>IFERROR(BDP(A15,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C15-AG15,"")</f>
         <v>0</v>
       </c>
       <c r="E15" s="18">
@@ -57590,83 +57590,83 @@
         <v>0</v>
       </c>
       <c r="N15">
-        <f>IFERROR(BDH(A15,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O15">
-        <f>IFERROR(BDH(A15,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P15">
-        <f>IFERROR(BDH(A15,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q15">
-        <f>IFERROR(BDH(A15,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R15">
-        <f>IFERROR(BDH(A15,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S15">
-        <f>IFERROR(BDH(A15,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T15">
-        <f>IFERROR(BDH(A15,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U15">
-        <f>IFERROR(BDH(A15,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V15">
-        <f>IFERROR(BDH(A15,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W15">
-        <f>IFERROR(BDH(A15,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X15">
-        <f>IFERROR(BDH(A15,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y15">
-        <f>IFERROR(BDH(A15,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z15">
-        <f>IFERROR(BDH(A15,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA15">
-        <f>IFERROR(BDH(A15,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB15">
-        <f>IFERROR(BDH(A15,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC15">
-        <f>IFERROR(BDH(A15,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD15">
-        <f>IFERROR(BDH(A15,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE15">
-        <f>IFERROR(BDH(A15,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF15">
-        <f>IFERROR(BDH(A15,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG15">
-        <f>IFERROR(BDH(A15,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -57684,7 +57684,7 @@
         <v>0</v>
       </c>
       <c r="D16" s="22">
-        <f>IFERROR(BDP(A16,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C16-AG16,"")</f>
         <v>0</v>
       </c>
       <c r="E16" s="23">
@@ -57720,83 +57720,83 @@
         <v>0</v>
       </c>
       <c r="N16">
-        <f>IFERROR(BDH(A16,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O16">
-        <f>IFERROR(BDH(A16,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P16">
-        <f>IFERROR(BDH(A16,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q16">
-        <f>IFERROR(BDH(A16,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R16">
-        <f>IFERROR(BDH(A16,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S16">
-        <f>IFERROR(BDH(A16,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T16">
-        <f>IFERROR(BDH(A16,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U16">
-        <f>IFERROR(BDH(A16,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V16">
-        <f>IFERROR(BDH(A16,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W16">
-        <f>IFERROR(BDH(A16,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X16">
-        <f>IFERROR(BDH(A16,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y16">
-        <f>IFERROR(BDH(A16,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z16">
-        <f>IFERROR(BDH(A16,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA16">
-        <f>IFERROR(BDH(A16,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB16">
-        <f>IFERROR(BDH(A16,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC16">
-        <f>IFERROR(BDH(A16,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD16">
-        <f>IFERROR(BDH(A16,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE16">
-        <f>IFERROR(BDH(A16,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF16">
-        <f>IFERROR(BDH(A16,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG16">
-        <f>IFERROR(BDH(A16,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -57814,7 +57814,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="17">
-        <f>IFERROR(BDP(A17,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C17-AG17,"")</f>
         <v>0</v>
       </c>
       <c r="E17" s="18">
@@ -57850,83 +57850,83 @@
         <v>0</v>
       </c>
       <c r="N17">
-        <f>IFERROR(BDH(A17,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O17">
-        <f>IFERROR(BDH(A17,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P17">
-        <f>IFERROR(BDH(A17,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q17">
-        <f>IFERROR(BDH(A17,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R17">
-        <f>IFERROR(BDH(A17,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S17">
-        <f>IFERROR(BDH(A17,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T17">
-        <f>IFERROR(BDH(A17,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U17">
-        <f>IFERROR(BDH(A17,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V17">
-        <f>IFERROR(BDH(A17,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W17">
-        <f>IFERROR(BDH(A17,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X17">
-        <f>IFERROR(BDH(A17,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y17">
-        <f>IFERROR(BDH(A17,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z17">
-        <f>IFERROR(BDH(A17,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA17">
-        <f>IFERROR(BDH(A17,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB17">
-        <f>IFERROR(BDH(A17,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC17">
-        <f>IFERROR(BDH(A17,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD17">
-        <f>IFERROR(BDH(A17,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE17">
-        <f>IFERROR(BDH(A17,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF17">
-        <f>IFERROR(BDH(A17,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG17">
-        <f>IFERROR(BDH(A17,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -65620,7 +65620,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="17">
-        <f>IFERROR(BDP(A3,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C3-AG3,"")</f>
         <v>0</v>
       </c>
       <c r="E3" s="18">
@@ -65656,83 +65656,83 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <f>IFERROR(BDH(A3,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O3">
-        <f>IFERROR(BDH(A3,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P3">
-        <f>IFERROR(BDH(A3,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q3">
-        <f>IFERROR(BDH(A3,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R3">
-        <f>IFERROR(BDH(A3,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S3">
-        <f>IFERROR(BDH(A3,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T3">
-        <f>IFERROR(BDH(A3,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U3">
-        <f>IFERROR(BDH(A3,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V3">
-        <f>IFERROR(BDH(A3,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W3">
-        <f>IFERROR(BDH(A3,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X3">
-        <f>IFERROR(BDH(A3,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y3">
-        <f>IFERROR(BDH(A3,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z3">
-        <f>IFERROR(BDH(A3,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA3">
-        <f>IFERROR(BDH(A3,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB3">
-        <f>IFERROR(BDH(A3,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC3">
-        <f>IFERROR(BDH(A3,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD3">
-        <f>IFERROR(BDH(A3,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE3">
-        <f>IFERROR(BDH(A3,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF3">
-        <f>IFERROR(BDH(A3,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG3">
-        <f>IFERROR(BDH(A3,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -65750,7 +65750,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="22">
-        <f>IFERROR(BDP(A4,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C4-AG4,"")</f>
         <v>0</v>
       </c>
       <c r="E4" s="23">
@@ -65786,83 +65786,83 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <f>IFERROR(BDH(A4,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O4">
-        <f>IFERROR(BDH(A4,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P4">
-        <f>IFERROR(BDH(A4,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q4">
-        <f>IFERROR(BDH(A4,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R4">
-        <f>IFERROR(BDH(A4,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S4">
-        <f>IFERROR(BDH(A4,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T4">
-        <f>IFERROR(BDH(A4,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U4">
-        <f>IFERROR(BDH(A4,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V4">
-        <f>IFERROR(BDH(A4,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W4">
-        <f>IFERROR(BDH(A4,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X4">
-        <f>IFERROR(BDH(A4,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y4">
-        <f>IFERROR(BDH(A4,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z4">
-        <f>IFERROR(BDH(A4,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA4">
-        <f>IFERROR(BDH(A4,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB4">
-        <f>IFERROR(BDH(A4,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC4">
-        <f>IFERROR(BDH(A4,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD4">
-        <f>IFERROR(BDH(A4,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE4">
-        <f>IFERROR(BDH(A4,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF4">
-        <f>IFERROR(BDH(A4,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG4">
-        <f>IFERROR(BDH(A4,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -65880,7 +65880,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="17">
-        <f>IFERROR(BDP(A5,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C5-AG5,"")</f>
         <v>0</v>
       </c>
       <c r="E5" s="18">
@@ -65916,83 +65916,83 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <f>IFERROR(BDH(A5,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O5">
-        <f>IFERROR(BDH(A5,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P5">
-        <f>IFERROR(BDH(A5,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q5">
-        <f>IFERROR(BDH(A5,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R5">
-        <f>IFERROR(BDH(A5,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S5">
-        <f>IFERROR(BDH(A5,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T5">
-        <f>IFERROR(BDH(A5,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U5">
-        <f>IFERROR(BDH(A5,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V5">
-        <f>IFERROR(BDH(A5,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W5">
-        <f>IFERROR(BDH(A5,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X5">
-        <f>IFERROR(BDH(A5,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y5">
-        <f>IFERROR(BDH(A5,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z5">
-        <f>IFERROR(BDH(A5,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA5">
-        <f>IFERROR(BDH(A5,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB5">
-        <f>IFERROR(BDH(A5,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC5">
-        <f>IFERROR(BDH(A5,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD5">
-        <f>IFERROR(BDH(A5,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE5">
-        <f>IFERROR(BDH(A5,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF5">
-        <f>IFERROR(BDH(A5,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG5">
-        <f>IFERROR(BDH(A5,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -66010,7 +66010,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="22">
-        <f>IFERROR(BDP(A6,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C6-AG6,"")</f>
         <v>0</v>
       </c>
       <c r="E6" s="23">
@@ -66046,83 +66046,83 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <f>IFERROR(BDH(A6,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O6">
-        <f>IFERROR(BDH(A6,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P6">
-        <f>IFERROR(BDH(A6,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q6">
-        <f>IFERROR(BDH(A6,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R6">
-        <f>IFERROR(BDH(A6,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S6">
-        <f>IFERROR(BDH(A6,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T6">
-        <f>IFERROR(BDH(A6,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U6">
-        <f>IFERROR(BDH(A6,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V6">
-        <f>IFERROR(BDH(A6,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W6">
-        <f>IFERROR(BDH(A6,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X6">
-        <f>IFERROR(BDH(A6,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y6">
-        <f>IFERROR(BDH(A6,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z6">
-        <f>IFERROR(BDH(A6,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA6">
-        <f>IFERROR(BDH(A6,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB6">
-        <f>IFERROR(BDH(A6,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC6">
-        <f>IFERROR(BDH(A6,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD6">
-        <f>IFERROR(BDH(A6,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE6">
-        <f>IFERROR(BDH(A6,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF6">
-        <f>IFERROR(BDH(A6,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG6">
-        <f>IFERROR(BDH(A6,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -66140,7 +66140,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="17">
-        <f>IFERROR(BDP(A7,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C7-AG7,"")</f>
         <v>0</v>
       </c>
       <c r="E7" s="18">
@@ -66176,83 +66176,83 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <f>IFERROR(BDH(A7,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O7">
-        <f>IFERROR(BDH(A7,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P7">
-        <f>IFERROR(BDH(A7,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q7">
-        <f>IFERROR(BDH(A7,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R7">
-        <f>IFERROR(BDH(A7,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S7">
-        <f>IFERROR(BDH(A7,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T7">
-        <f>IFERROR(BDH(A7,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U7">
-        <f>IFERROR(BDH(A7,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V7">
-        <f>IFERROR(BDH(A7,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W7">
-        <f>IFERROR(BDH(A7,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X7">
-        <f>IFERROR(BDH(A7,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y7">
-        <f>IFERROR(BDH(A7,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z7">
-        <f>IFERROR(BDH(A7,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA7">
-        <f>IFERROR(BDH(A7,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB7">
-        <f>IFERROR(BDH(A7,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC7">
-        <f>IFERROR(BDH(A7,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD7">
-        <f>IFERROR(BDH(A7,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE7">
-        <f>IFERROR(BDH(A7,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF7">
-        <f>IFERROR(BDH(A7,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG7">
-        <f>IFERROR(BDH(A7,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -66270,7 +66270,7 @@
         <v>0</v>
       </c>
       <c r="D8" s="22">
-        <f>IFERROR(BDP(A8,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C8-AG8,"")</f>
         <v>0</v>
       </c>
       <c r="E8" s="23">
@@ -66306,83 +66306,83 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <f>IFERROR(BDH(A8,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O8">
-        <f>IFERROR(BDH(A8,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P8">
-        <f>IFERROR(BDH(A8,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q8">
-        <f>IFERROR(BDH(A8,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R8">
-        <f>IFERROR(BDH(A8,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S8">
-        <f>IFERROR(BDH(A8,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T8">
-        <f>IFERROR(BDH(A8,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U8">
-        <f>IFERROR(BDH(A8,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V8">
-        <f>IFERROR(BDH(A8,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W8">
-        <f>IFERROR(BDH(A8,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X8">
-        <f>IFERROR(BDH(A8,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y8">
-        <f>IFERROR(BDH(A8,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z8">
-        <f>IFERROR(BDH(A8,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA8">
-        <f>IFERROR(BDH(A8,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB8">
-        <f>IFERROR(BDH(A8,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC8">
-        <f>IFERROR(BDH(A8,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD8">
-        <f>IFERROR(BDH(A8,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE8">
-        <f>IFERROR(BDH(A8,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF8">
-        <f>IFERROR(BDH(A8,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG8">
-        <f>IFERROR(BDH(A8,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -66400,7 +66400,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="17">
-        <f>IFERROR(BDP(A9,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C9-AG9,"")</f>
         <v>0</v>
       </c>
       <c r="E9" s="18">
@@ -66436,83 +66436,83 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <f>IFERROR(BDH(A9,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O9">
-        <f>IFERROR(BDH(A9,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P9">
-        <f>IFERROR(BDH(A9,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q9">
-        <f>IFERROR(BDH(A9,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R9">
-        <f>IFERROR(BDH(A9,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S9">
-        <f>IFERROR(BDH(A9,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T9">
-        <f>IFERROR(BDH(A9,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U9">
-        <f>IFERROR(BDH(A9,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V9">
-        <f>IFERROR(BDH(A9,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W9">
-        <f>IFERROR(BDH(A9,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X9">
-        <f>IFERROR(BDH(A9,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y9">
-        <f>IFERROR(BDH(A9,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z9">
-        <f>IFERROR(BDH(A9,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA9">
-        <f>IFERROR(BDH(A9,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB9">
-        <f>IFERROR(BDH(A9,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC9">
-        <f>IFERROR(BDH(A9,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD9">
-        <f>IFERROR(BDH(A9,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE9">
-        <f>IFERROR(BDH(A9,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF9">
-        <f>IFERROR(BDH(A9,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG9">
-        <f>IFERROR(BDH(A9,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -66530,7 +66530,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="22">
-        <f>IFERROR(BDP(A10,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C10-AG10,"")</f>
         <v>0</v>
       </c>
       <c r="E10" s="23">
@@ -66566,83 +66566,83 @@
         <v>0</v>
       </c>
       <c r="N10">
-        <f>IFERROR(BDH(A10,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O10">
-        <f>IFERROR(BDH(A10,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P10">
-        <f>IFERROR(BDH(A10,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q10">
-        <f>IFERROR(BDH(A10,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R10">
-        <f>IFERROR(BDH(A10,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S10">
-        <f>IFERROR(BDH(A10,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T10">
-        <f>IFERROR(BDH(A10,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U10">
-        <f>IFERROR(BDH(A10,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V10">
-        <f>IFERROR(BDH(A10,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W10">
-        <f>IFERROR(BDH(A10,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X10">
-        <f>IFERROR(BDH(A10,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y10">
-        <f>IFERROR(BDH(A10,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z10">
-        <f>IFERROR(BDH(A10,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA10">
-        <f>IFERROR(BDH(A10,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB10">
-        <f>IFERROR(BDH(A10,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC10">
-        <f>IFERROR(BDH(A10,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD10">
-        <f>IFERROR(BDH(A10,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE10">
-        <f>IFERROR(BDH(A10,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF10">
-        <f>IFERROR(BDH(A10,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG10">
-        <f>IFERROR(BDH(A10,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -66660,7 +66660,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="17">
-        <f>IFERROR(BDP(A11,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C11-AG11,"")</f>
         <v>0</v>
       </c>
       <c r="E11" s="18">
@@ -66696,83 +66696,83 @@
         <v>0</v>
       </c>
       <c r="N11">
-        <f>IFERROR(BDH(A11,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O11">
-        <f>IFERROR(BDH(A11,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P11">
-        <f>IFERROR(BDH(A11,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q11">
-        <f>IFERROR(BDH(A11,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R11">
-        <f>IFERROR(BDH(A11,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S11">
-        <f>IFERROR(BDH(A11,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T11">
-        <f>IFERROR(BDH(A11,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U11">
-        <f>IFERROR(BDH(A11,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V11">
-        <f>IFERROR(BDH(A11,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W11">
-        <f>IFERROR(BDH(A11,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X11">
-        <f>IFERROR(BDH(A11,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y11">
-        <f>IFERROR(BDH(A11,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z11">
-        <f>IFERROR(BDH(A11,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA11">
-        <f>IFERROR(BDH(A11,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB11">
-        <f>IFERROR(BDH(A11,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC11">
-        <f>IFERROR(BDH(A11,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD11">
-        <f>IFERROR(BDH(A11,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE11">
-        <f>IFERROR(BDH(A11,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF11">
-        <f>IFERROR(BDH(A11,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG11">
-        <f>IFERROR(BDH(A11,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -66790,7 +66790,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="22">
-        <f>IFERROR(BDP(A12,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C12-AG12,"")</f>
         <v>0</v>
       </c>
       <c r="E12" s="23">
@@ -66826,83 +66826,83 @@
         <v>0</v>
       </c>
       <c r="N12">
-        <f>IFERROR(BDH(A12,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O12">
-        <f>IFERROR(BDH(A12,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P12">
-        <f>IFERROR(BDH(A12,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q12">
-        <f>IFERROR(BDH(A12,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R12">
-        <f>IFERROR(BDH(A12,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S12">
-        <f>IFERROR(BDH(A12,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T12">
-        <f>IFERROR(BDH(A12,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U12">
-        <f>IFERROR(BDH(A12,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V12">
-        <f>IFERROR(BDH(A12,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W12">
-        <f>IFERROR(BDH(A12,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X12">
-        <f>IFERROR(BDH(A12,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y12">
-        <f>IFERROR(BDH(A12,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z12">
-        <f>IFERROR(BDH(A12,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA12">
-        <f>IFERROR(BDH(A12,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB12">
-        <f>IFERROR(BDH(A12,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC12">
-        <f>IFERROR(BDH(A12,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD12">
-        <f>IFERROR(BDH(A12,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE12">
-        <f>IFERROR(BDH(A12,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF12">
-        <f>IFERROR(BDH(A12,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG12">
-        <f>IFERROR(BDH(A12,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -66920,7 +66920,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="17">
-        <f>IFERROR(BDP(A13,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C13-AG13,"")</f>
         <v>0</v>
       </c>
       <c r="E13" s="18">
@@ -66956,83 +66956,83 @@
         <v>0</v>
       </c>
       <c r="N13">
-        <f>IFERROR(BDH(A13,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O13">
-        <f>IFERROR(BDH(A13,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P13">
-        <f>IFERROR(BDH(A13,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q13">
-        <f>IFERROR(BDH(A13,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R13">
-        <f>IFERROR(BDH(A13,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S13">
-        <f>IFERROR(BDH(A13,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T13">
-        <f>IFERROR(BDH(A13,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U13">
-        <f>IFERROR(BDH(A13,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V13">
-        <f>IFERROR(BDH(A13,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W13">
-        <f>IFERROR(BDH(A13,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X13">
-        <f>IFERROR(BDH(A13,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y13">
-        <f>IFERROR(BDH(A13,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z13">
-        <f>IFERROR(BDH(A13,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA13">
-        <f>IFERROR(BDH(A13,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB13">
-        <f>IFERROR(BDH(A13,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC13">
-        <f>IFERROR(BDH(A13,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD13">
-        <f>IFERROR(BDH(A13,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE13">
-        <f>IFERROR(BDH(A13,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF13">
-        <f>IFERROR(BDH(A13,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG13">
-        <f>IFERROR(BDH(A13,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -67050,7 +67050,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="22">
-        <f>IFERROR(BDP(A14,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C14-AG14,"")</f>
         <v>0</v>
       </c>
       <c r="E14" s="23">
@@ -67086,83 +67086,83 @@
         <v>0</v>
       </c>
       <c r="N14">
-        <f>IFERROR(BDH(A14,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O14">
-        <f>IFERROR(BDH(A14,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P14">
-        <f>IFERROR(BDH(A14,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q14">
-        <f>IFERROR(BDH(A14,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R14">
-        <f>IFERROR(BDH(A14,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S14">
-        <f>IFERROR(BDH(A14,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T14">
-        <f>IFERROR(BDH(A14,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U14">
-        <f>IFERROR(BDH(A14,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V14">
-        <f>IFERROR(BDH(A14,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W14">
-        <f>IFERROR(BDH(A14,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X14">
-        <f>IFERROR(BDH(A14,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y14">
-        <f>IFERROR(BDH(A14,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z14">
-        <f>IFERROR(BDH(A14,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA14">
-        <f>IFERROR(BDH(A14,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB14">
-        <f>IFERROR(BDH(A14,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC14">
-        <f>IFERROR(BDH(A14,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD14">
-        <f>IFERROR(BDH(A14,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE14">
-        <f>IFERROR(BDH(A14,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF14">
-        <f>IFERROR(BDH(A14,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG14">
-        <f>IFERROR(BDH(A14,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -67180,7 +67180,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="17">
-        <f>IFERROR(BDP(A15,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C15-AG15,"")</f>
         <v>0</v>
       </c>
       <c r="E15" s="18">
@@ -67216,83 +67216,83 @@
         <v>0</v>
       </c>
       <c r="N15">
-        <f>IFERROR(BDH(A15,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O15">
-        <f>IFERROR(BDH(A15,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P15">
-        <f>IFERROR(BDH(A15,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q15">
-        <f>IFERROR(BDH(A15,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R15">
-        <f>IFERROR(BDH(A15,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S15">
-        <f>IFERROR(BDH(A15,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T15">
-        <f>IFERROR(BDH(A15,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U15">
-        <f>IFERROR(BDH(A15,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V15">
-        <f>IFERROR(BDH(A15,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W15">
-        <f>IFERROR(BDH(A15,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X15">
-        <f>IFERROR(BDH(A15,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y15">
-        <f>IFERROR(BDH(A15,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z15">
-        <f>IFERROR(BDH(A15,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA15">
-        <f>IFERROR(BDH(A15,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB15">
-        <f>IFERROR(BDH(A15,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC15">
-        <f>IFERROR(BDH(A15,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD15">
-        <f>IFERROR(BDH(A15,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE15">
-        <f>IFERROR(BDH(A15,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF15">
-        <f>IFERROR(BDH(A15,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG15">
-        <f>IFERROR(BDH(A15,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -67310,7 +67310,7 @@
         <v>0</v>
       </c>
       <c r="D16" s="22">
-        <f>IFERROR(BDP(A16,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C16-AG16,"")</f>
         <v>0</v>
       </c>
       <c r="E16" s="23">
@@ -67346,83 +67346,83 @@
         <v>0</v>
       </c>
       <c r="N16">
-        <f>IFERROR(BDH(A16,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O16">
-        <f>IFERROR(BDH(A16,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P16">
-        <f>IFERROR(BDH(A16,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q16">
-        <f>IFERROR(BDH(A16,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R16">
-        <f>IFERROR(BDH(A16,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S16">
-        <f>IFERROR(BDH(A16,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T16">
-        <f>IFERROR(BDH(A16,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U16">
-        <f>IFERROR(BDH(A16,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V16">
-        <f>IFERROR(BDH(A16,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W16">
-        <f>IFERROR(BDH(A16,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X16">
-        <f>IFERROR(BDH(A16,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y16">
-        <f>IFERROR(BDH(A16,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z16">
-        <f>IFERROR(BDH(A16,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA16">
-        <f>IFERROR(BDH(A16,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB16">
-        <f>IFERROR(BDH(A16,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC16">
-        <f>IFERROR(BDH(A16,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD16">
-        <f>IFERROR(BDH(A16,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE16">
-        <f>IFERROR(BDH(A16,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF16">
-        <f>IFERROR(BDH(A16,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG16">
-        <f>IFERROR(BDH(A16,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -67440,7 +67440,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="17">
-        <f>IFERROR(BDP(A17,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C17-AG17,"")</f>
         <v>0</v>
       </c>
       <c r="E17" s="18">
@@ -67476,83 +67476,83 @@
         <v>0</v>
       </c>
       <c r="N17">
-        <f>IFERROR(BDH(A17,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O17">
-        <f>IFERROR(BDH(A17,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P17">
-        <f>IFERROR(BDH(A17,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q17">
-        <f>IFERROR(BDH(A17,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R17">
-        <f>IFERROR(BDH(A17,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S17">
-        <f>IFERROR(BDH(A17,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T17">
-        <f>IFERROR(BDH(A17,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U17">
-        <f>IFERROR(BDH(A17,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V17">
-        <f>IFERROR(BDH(A17,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W17">
-        <f>IFERROR(BDH(A17,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X17">
-        <f>IFERROR(BDH(A17,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y17">
-        <f>IFERROR(BDH(A17,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z17">
-        <f>IFERROR(BDH(A17,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA17">
-        <f>IFERROR(BDH(A17,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB17">
-        <f>IFERROR(BDH(A17,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC17">
-        <f>IFERROR(BDH(A17,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD17">
-        <f>IFERROR(BDH(A17,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE17">
-        <f>IFERROR(BDH(A17,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF17">
-        <f>IFERROR(BDH(A17,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG17">
-        <f>IFERROR(BDH(A17,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -74158,7 +74158,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="17">
-        <f>IFERROR(BDP(A3,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C3-AG3,"")</f>
         <v>0</v>
       </c>
       <c r="E3" s="18">
@@ -74194,83 +74194,83 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <f>IFERROR(BDH(A3,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O3">
-        <f>IFERROR(BDH(A3,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P3">
-        <f>IFERROR(BDH(A3,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q3">
-        <f>IFERROR(BDH(A3,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R3">
-        <f>IFERROR(BDH(A3,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S3">
-        <f>IFERROR(BDH(A3,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T3">
-        <f>IFERROR(BDH(A3,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U3">
-        <f>IFERROR(BDH(A3,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V3">
-        <f>IFERROR(BDH(A3,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W3">
-        <f>IFERROR(BDH(A3,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X3">
-        <f>IFERROR(BDH(A3,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y3">
-        <f>IFERROR(BDH(A3,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z3">
-        <f>IFERROR(BDH(A3,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA3">
-        <f>IFERROR(BDH(A3,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB3">
-        <f>IFERROR(BDH(A3,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC3">
-        <f>IFERROR(BDH(A3,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD3">
-        <f>IFERROR(BDH(A3,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE3">
-        <f>IFERROR(BDH(A3,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF3">
-        <f>IFERROR(BDH(A3,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG3">
-        <f>IFERROR(BDH(A3,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -74288,7 +74288,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="22">
-        <f>IFERROR(BDP(A4,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C4-AG4,"")</f>
         <v>0</v>
       </c>
       <c r="E4" s="23">
@@ -74324,83 +74324,83 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <f>IFERROR(BDH(A4,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O4">
-        <f>IFERROR(BDH(A4,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P4">
-        <f>IFERROR(BDH(A4,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q4">
-        <f>IFERROR(BDH(A4,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R4">
-        <f>IFERROR(BDH(A4,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S4">
-        <f>IFERROR(BDH(A4,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T4">
-        <f>IFERROR(BDH(A4,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U4">
-        <f>IFERROR(BDH(A4,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V4">
-        <f>IFERROR(BDH(A4,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W4">
-        <f>IFERROR(BDH(A4,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X4">
-        <f>IFERROR(BDH(A4,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y4">
-        <f>IFERROR(BDH(A4,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z4">
-        <f>IFERROR(BDH(A4,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA4">
-        <f>IFERROR(BDH(A4,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB4">
-        <f>IFERROR(BDH(A4,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC4">
-        <f>IFERROR(BDH(A4,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD4">
-        <f>IFERROR(BDH(A4,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE4">
-        <f>IFERROR(BDH(A4,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF4">
-        <f>IFERROR(BDH(A4,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG4">
-        <f>IFERROR(BDH(A4,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -74418,7 +74418,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="17">
-        <f>IFERROR(BDP(A5,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C5-AG5,"")</f>
         <v>0</v>
       </c>
       <c r="E5" s="18">
@@ -74454,83 +74454,83 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <f>IFERROR(BDH(A5,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O5">
-        <f>IFERROR(BDH(A5,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P5">
-        <f>IFERROR(BDH(A5,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q5">
-        <f>IFERROR(BDH(A5,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R5">
-        <f>IFERROR(BDH(A5,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S5">
-        <f>IFERROR(BDH(A5,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T5">
-        <f>IFERROR(BDH(A5,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U5">
-        <f>IFERROR(BDH(A5,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V5">
-        <f>IFERROR(BDH(A5,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W5">
-        <f>IFERROR(BDH(A5,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X5">
-        <f>IFERROR(BDH(A5,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y5">
-        <f>IFERROR(BDH(A5,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z5">
-        <f>IFERROR(BDH(A5,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA5">
-        <f>IFERROR(BDH(A5,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB5">
-        <f>IFERROR(BDH(A5,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC5">
-        <f>IFERROR(BDH(A5,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD5">
-        <f>IFERROR(BDH(A5,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE5">
-        <f>IFERROR(BDH(A5,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF5">
-        <f>IFERROR(BDH(A5,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG5">
-        <f>IFERROR(BDH(A5,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -74548,7 +74548,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="22">
-        <f>IFERROR(BDP(A6,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C6-AG6,"")</f>
         <v>0</v>
       </c>
       <c r="E6" s="23">
@@ -74584,83 +74584,83 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <f>IFERROR(BDH(A6,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O6">
-        <f>IFERROR(BDH(A6,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P6">
-        <f>IFERROR(BDH(A6,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q6">
-        <f>IFERROR(BDH(A6,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R6">
-        <f>IFERROR(BDH(A6,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S6">
-        <f>IFERROR(BDH(A6,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T6">
-        <f>IFERROR(BDH(A6,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U6">
-        <f>IFERROR(BDH(A6,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V6">
-        <f>IFERROR(BDH(A6,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W6">
-        <f>IFERROR(BDH(A6,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X6">
-        <f>IFERROR(BDH(A6,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y6">
-        <f>IFERROR(BDH(A6,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z6">
-        <f>IFERROR(BDH(A6,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA6">
-        <f>IFERROR(BDH(A6,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB6">
-        <f>IFERROR(BDH(A6,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC6">
-        <f>IFERROR(BDH(A6,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD6">
-        <f>IFERROR(BDH(A6,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE6">
-        <f>IFERROR(BDH(A6,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF6">
-        <f>IFERROR(BDH(A6,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG6">
-        <f>IFERROR(BDH(A6,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -74678,7 +74678,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="17">
-        <f>IFERROR(BDP(A7,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C7-AG7,"")</f>
         <v>0</v>
       </c>
       <c r="E7" s="18">
@@ -74714,83 +74714,83 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <f>IFERROR(BDH(A7,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O7">
-        <f>IFERROR(BDH(A7,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P7">
-        <f>IFERROR(BDH(A7,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q7">
-        <f>IFERROR(BDH(A7,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R7">
-        <f>IFERROR(BDH(A7,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S7">
-        <f>IFERROR(BDH(A7,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T7">
-        <f>IFERROR(BDH(A7,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U7">
-        <f>IFERROR(BDH(A7,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V7">
-        <f>IFERROR(BDH(A7,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W7">
-        <f>IFERROR(BDH(A7,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X7">
-        <f>IFERROR(BDH(A7,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y7">
-        <f>IFERROR(BDH(A7,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z7">
-        <f>IFERROR(BDH(A7,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA7">
-        <f>IFERROR(BDH(A7,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB7">
-        <f>IFERROR(BDH(A7,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC7">
-        <f>IFERROR(BDH(A7,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD7">
-        <f>IFERROR(BDH(A7,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE7">
-        <f>IFERROR(BDH(A7,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF7">
-        <f>IFERROR(BDH(A7,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG7">
-        <f>IFERROR(BDH(A7,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -74808,7 +74808,7 @@
         <v>0</v>
       </c>
       <c r="D8" s="22">
-        <f>IFERROR(BDP(A8,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C8-AG8,"")</f>
         <v>0</v>
       </c>
       <c r="E8" s="23">
@@ -74844,83 +74844,83 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <f>IFERROR(BDH(A8,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O8">
-        <f>IFERROR(BDH(A8,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P8">
-        <f>IFERROR(BDH(A8,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q8">
-        <f>IFERROR(BDH(A8,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R8">
-        <f>IFERROR(BDH(A8,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S8">
-        <f>IFERROR(BDH(A8,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T8">
-        <f>IFERROR(BDH(A8,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U8">
-        <f>IFERROR(BDH(A8,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V8">
-        <f>IFERROR(BDH(A8,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W8">
-        <f>IFERROR(BDH(A8,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X8">
-        <f>IFERROR(BDH(A8,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y8">
-        <f>IFERROR(BDH(A8,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z8">
-        <f>IFERROR(BDH(A8,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA8">
-        <f>IFERROR(BDH(A8,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB8">
-        <f>IFERROR(BDH(A8,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC8">
-        <f>IFERROR(BDH(A8,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD8">
-        <f>IFERROR(BDH(A8,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE8">
-        <f>IFERROR(BDH(A8,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF8">
-        <f>IFERROR(BDH(A8,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG8">
-        <f>IFERROR(BDH(A8,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -74938,7 +74938,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="17">
-        <f>IFERROR(BDP(A9,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C9-AG9,"")</f>
         <v>0</v>
       </c>
       <c r="E9" s="18">
@@ -74974,83 +74974,83 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <f>IFERROR(BDH(A9,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O9">
-        <f>IFERROR(BDH(A9,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P9">
-        <f>IFERROR(BDH(A9,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q9">
-        <f>IFERROR(BDH(A9,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R9">
-        <f>IFERROR(BDH(A9,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S9">
-        <f>IFERROR(BDH(A9,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T9">
-        <f>IFERROR(BDH(A9,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U9">
-        <f>IFERROR(BDH(A9,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V9">
-        <f>IFERROR(BDH(A9,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W9">
-        <f>IFERROR(BDH(A9,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X9">
-        <f>IFERROR(BDH(A9,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y9">
-        <f>IFERROR(BDH(A9,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z9">
-        <f>IFERROR(BDH(A9,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA9">
-        <f>IFERROR(BDH(A9,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB9">
-        <f>IFERROR(BDH(A9,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC9">
-        <f>IFERROR(BDH(A9,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD9">
-        <f>IFERROR(BDH(A9,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE9">
-        <f>IFERROR(BDH(A9,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF9">
-        <f>IFERROR(BDH(A9,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG9">
-        <f>IFERROR(BDH(A9,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -75068,7 +75068,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="22">
-        <f>IFERROR(BDP(A10,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C10-AG10,"")</f>
         <v>0</v>
       </c>
       <c r="E10" s="23">
@@ -75104,83 +75104,83 @@
         <v>0</v>
       </c>
       <c r="N10">
-        <f>IFERROR(BDH(A10,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O10">
-        <f>IFERROR(BDH(A10,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P10">
-        <f>IFERROR(BDH(A10,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q10">
-        <f>IFERROR(BDH(A10,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R10">
-        <f>IFERROR(BDH(A10,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S10">
-        <f>IFERROR(BDH(A10,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T10">
-        <f>IFERROR(BDH(A10,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U10">
-        <f>IFERROR(BDH(A10,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V10">
-        <f>IFERROR(BDH(A10,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W10">
-        <f>IFERROR(BDH(A10,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X10">
-        <f>IFERROR(BDH(A10,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y10">
-        <f>IFERROR(BDH(A10,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z10">
-        <f>IFERROR(BDH(A10,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA10">
-        <f>IFERROR(BDH(A10,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB10">
-        <f>IFERROR(BDH(A10,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC10">
-        <f>IFERROR(BDH(A10,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD10">
-        <f>IFERROR(BDH(A10,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE10">
-        <f>IFERROR(BDH(A10,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF10">
-        <f>IFERROR(BDH(A10,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG10">
-        <f>IFERROR(BDH(A10,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -75198,7 +75198,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="17">
-        <f>IFERROR(BDP(A11,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C11-AG11,"")</f>
         <v>0</v>
       </c>
       <c r="E11" s="18">
@@ -75234,83 +75234,83 @@
         <v>0</v>
       </c>
       <c r="N11">
-        <f>IFERROR(BDH(A11,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O11">
-        <f>IFERROR(BDH(A11,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P11">
-        <f>IFERROR(BDH(A11,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q11">
-        <f>IFERROR(BDH(A11,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R11">
-        <f>IFERROR(BDH(A11,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S11">
-        <f>IFERROR(BDH(A11,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T11">
-        <f>IFERROR(BDH(A11,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U11">
-        <f>IFERROR(BDH(A11,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V11">
-        <f>IFERROR(BDH(A11,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W11">
-        <f>IFERROR(BDH(A11,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X11">
-        <f>IFERROR(BDH(A11,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y11">
-        <f>IFERROR(BDH(A11,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z11">
-        <f>IFERROR(BDH(A11,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA11">
-        <f>IFERROR(BDH(A11,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB11">
-        <f>IFERROR(BDH(A11,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC11">
-        <f>IFERROR(BDH(A11,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD11">
-        <f>IFERROR(BDH(A11,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE11">
-        <f>IFERROR(BDH(A11,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF11">
-        <f>IFERROR(BDH(A11,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG11">
-        <f>IFERROR(BDH(A11,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -75328,7 +75328,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="22">
-        <f>IFERROR(BDP(A12,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C12-AG12,"")</f>
         <v>0</v>
       </c>
       <c r="E12" s="23">
@@ -75364,83 +75364,83 @@
         <v>0</v>
       </c>
       <c r="N12">
-        <f>IFERROR(BDH(A12,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O12">
-        <f>IFERROR(BDH(A12,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P12">
-        <f>IFERROR(BDH(A12,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q12">
-        <f>IFERROR(BDH(A12,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R12">
-        <f>IFERROR(BDH(A12,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S12">
-        <f>IFERROR(BDH(A12,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T12">
-        <f>IFERROR(BDH(A12,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U12">
-        <f>IFERROR(BDH(A12,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V12">
-        <f>IFERROR(BDH(A12,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W12">
-        <f>IFERROR(BDH(A12,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X12">
-        <f>IFERROR(BDH(A12,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y12">
-        <f>IFERROR(BDH(A12,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z12">
-        <f>IFERROR(BDH(A12,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA12">
-        <f>IFERROR(BDH(A12,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB12">
-        <f>IFERROR(BDH(A12,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC12">
-        <f>IFERROR(BDH(A12,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD12">
-        <f>IFERROR(BDH(A12,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE12">
-        <f>IFERROR(BDH(A12,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF12">
-        <f>IFERROR(BDH(A12,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG12">
-        <f>IFERROR(BDH(A12,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -75458,7 +75458,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="17">
-        <f>IFERROR(BDP(A13,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C13-AG13,"")</f>
         <v>0</v>
       </c>
       <c r="E13" s="18">
@@ -75494,83 +75494,83 @@
         <v>0</v>
       </c>
       <c r="N13">
-        <f>IFERROR(BDH(A13,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O13">
-        <f>IFERROR(BDH(A13,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P13">
-        <f>IFERROR(BDH(A13,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q13">
-        <f>IFERROR(BDH(A13,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R13">
-        <f>IFERROR(BDH(A13,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S13">
-        <f>IFERROR(BDH(A13,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T13">
-        <f>IFERROR(BDH(A13,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U13">
-        <f>IFERROR(BDH(A13,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V13">
-        <f>IFERROR(BDH(A13,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W13">
-        <f>IFERROR(BDH(A13,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X13">
-        <f>IFERROR(BDH(A13,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y13">
-        <f>IFERROR(BDH(A13,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z13">
-        <f>IFERROR(BDH(A13,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA13">
-        <f>IFERROR(BDH(A13,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB13">
-        <f>IFERROR(BDH(A13,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC13">
-        <f>IFERROR(BDH(A13,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD13">
-        <f>IFERROR(BDH(A13,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE13">
-        <f>IFERROR(BDH(A13,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF13">
-        <f>IFERROR(BDH(A13,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG13">
-        <f>IFERROR(BDH(A13,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -75588,7 +75588,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="22">
-        <f>IFERROR(BDP(A14,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C14-AG14,"")</f>
         <v>0</v>
       </c>
       <c r="E14" s="23">
@@ -75624,83 +75624,83 @@
         <v>0</v>
       </c>
       <c r="N14">
-        <f>IFERROR(BDH(A14,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O14">
-        <f>IFERROR(BDH(A14,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P14">
-        <f>IFERROR(BDH(A14,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q14">
-        <f>IFERROR(BDH(A14,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R14">
-        <f>IFERROR(BDH(A14,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S14">
-        <f>IFERROR(BDH(A14,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T14">
-        <f>IFERROR(BDH(A14,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U14">
-        <f>IFERROR(BDH(A14,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V14">
-        <f>IFERROR(BDH(A14,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W14">
-        <f>IFERROR(BDH(A14,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X14">
-        <f>IFERROR(BDH(A14,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y14">
-        <f>IFERROR(BDH(A14,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z14">
-        <f>IFERROR(BDH(A14,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA14">
-        <f>IFERROR(BDH(A14,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB14">
-        <f>IFERROR(BDH(A14,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC14">
-        <f>IFERROR(BDH(A14,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD14">
-        <f>IFERROR(BDH(A14,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE14">
-        <f>IFERROR(BDH(A14,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF14">
-        <f>IFERROR(BDH(A14,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG14">
-        <f>IFERROR(BDH(A14,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -75718,7 +75718,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="17">
-        <f>IFERROR(BDP(A15,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C15-AG15,"")</f>
         <v>0</v>
       </c>
       <c r="E15" s="18">
@@ -75754,83 +75754,83 @@
         <v>0</v>
       </c>
       <c r="N15">
-        <f>IFERROR(BDH(A15,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O15">
-        <f>IFERROR(BDH(A15,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P15">
-        <f>IFERROR(BDH(A15,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q15">
-        <f>IFERROR(BDH(A15,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R15">
-        <f>IFERROR(BDH(A15,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S15">
-        <f>IFERROR(BDH(A15,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T15">
-        <f>IFERROR(BDH(A15,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U15">
-        <f>IFERROR(BDH(A15,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V15">
-        <f>IFERROR(BDH(A15,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W15">
-        <f>IFERROR(BDH(A15,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X15">
-        <f>IFERROR(BDH(A15,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y15">
-        <f>IFERROR(BDH(A15,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z15">
-        <f>IFERROR(BDH(A15,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA15">
-        <f>IFERROR(BDH(A15,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB15">
-        <f>IFERROR(BDH(A15,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC15">
-        <f>IFERROR(BDH(A15,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD15">
-        <f>IFERROR(BDH(A15,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE15">
-        <f>IFERROR(BDH(A15,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF15">
-        <f>IFERROR(BDH(A15,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG15">
-        <f>IFERROR(BDH(A15,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -75848,7 +75848,7 @@
         <v>0</v>
       </c>
       <c r="D16" s="22">
-        <f>IFERROR(BDP(A16,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C16-AG16,"")</f>
         <v>0</v>
       </c>
       <c r="E16" s="23">
@@ -75884,83 +75884,83 @@
         <v>0</v>
       </c>
       <c r="N16">
-        <f>IFERROR(BDH(A16,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O16">
-        <f>IFERROR(BDH(A16,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P16">
-        <f>IFERROR(BDH(A16,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q16">
-        <f>IFERROR(BDH(A16,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R16">
-        <f>IFERROR(BDH(A16,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S16">
-        <f>IFERROR(BDH(A16,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T16">
-        <f>IFERROR(BDH(A16,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U16">
-        <f>IFERROR(BDH(A16,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V16">
-        <f>IFERROR(BDH(A16,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W16">
-        <f>IFERROR(BDH(A16,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X16">
-        <f>IFERROR(BDH(A16,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y16">
-        <f>IFERROR(BDH(A16,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z16">
-        <f>IFERROR(BDH(A16,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA16">
-        <f>IFERROR(BDH(A16,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB16">
-        <f>IFERROR(BDH(A16,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC16">
-        <f>IFERROR(BDH(A16,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD16">
-        <f>IFERROR(BDH(A16,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE16">
-        <f>IFERROR(BDH(A16,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF16">
-        <f>IFERROR(BDH(A16,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG16">
-        <f>IFERROR(BDH(A16,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -75978,7 +75978,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="17">
-        <f>IFERROR(BDP(A17,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C17-AG17,"")</f>
         <v>0</v>
       </c>
       <c r="E17" s="18">
@@ -76014,83 +76014,83 @@
         <v>0</v>
       </c>
       <c r="N17">
-        <f>IFERROR(BDH(A17,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O17">
-        <f>IFERROR(BDH(A17,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P17">
-        <f>IFERROR(BDH(A17,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q17">
-        <f>IFERROR(BDH(A17,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R17">
-        <f>IFERROR(BDH(A17,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S17">
-        <f>IFERROR(BDH(A17,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T17">
-        <f>IFERROR(BDH(A17,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U17">
-        <f>IFERROR(BDH(A17,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V17">
-        <f>IFERROR(BDH(A17,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W17">
-        <f>IFERROR(BDH(A17,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X17">
-        <f>IFERROR(BDH(A17,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y17">
-        <f>IFERROR(BDH(A17,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z17">
-        <f>IFERROR(BDH(A17,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA17">
-        <f>IFERROR(BDH(A17,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB17">
-        <f>IFERROR(BDH(A17,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC17">
-        <f>IFERROR(BDH(A17,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD17">
-        <f>IFERROR(BDH(A17,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE17">
-        <f>IFERROR(BDH(A17,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF17">
-        <f>IFERROR(BDH(A17,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG17">
-        <f>IFERROR(BDH(A17,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -82152,7 +82152,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="17">
-        <f>IFERROR(BDP(A3,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C3-AG3,"")</f>
         <v>0</v>
       </c>
       <c r="E3" s="18">
@@ -82188,83 +82188,83 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <f>IFERROR(BDH(A3,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O3">
-        <f>IFERROR(BDH(A3,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P3">
-        <f>IFERROR(BDH(A3,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q3">
-        <f>IFERROR(BDH(A3,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R3">
-        <f>IFERROR(BDH(A3,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S3">
-        <f>IFERROR(BDH(A3,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T3">
-        <f>IFERROR(BDH(A3,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U3">
-        <f>IFERROR(BDH(A3,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V3">
-        <f>IFERROR(BDH(A3,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W3">
-        <f>IFERROR(BDH(A3,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X3">
-        <f>IFERROR(BDH(A3,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y3">
-        <f>IFERROR(BDH(A3,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z3">
-        <f>IFERROR(BDH(A3,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA3">
-        <f>IFERROR(BDH(A3,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB3">
-        <f>IFERROR(BDH(A3,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC3">
-        <f>IFERROR(BDH(A3,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD3">
-        <f>IFERROR(BDH(A3,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE3">
-        <f>IFERROR(BDH(A3,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF3">
-        <f>IFERROR(BDH(A3,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG3">
-        <f>IFERROR(BDH(A3,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -82282,7 +82282,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="22">
-        <f>IFERROR(BDP(A4,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C4-AG4,"")</f>
         <v>0</v>
       </c>
       <c r="E4" s="23">
@@ -82318,83 +82318,83 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <f>IFERROR(BDH(A4,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O4">
-        <f>IFERROR(BDH(A4,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P4">
-        <f>IFERROR(BDH(A4,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q4">
-        <f>IFERROR(BDH(A4,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R4">
-        <f>IFERROR(BDH(A4,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S4">
-        <f>IFERROR(BDH(A4,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T4">
-        <f>IFERROR(BDH(A4,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U4">
-        <f>IFERROR(BDH(A4,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V4">
-        <f>IFERROR(BDH(A4,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W4">
-        <f>IFERROR(BDH(A4,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X4">
-        <f>IFERROR(BDH(A4,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y4">
-        <f>IFERROR(BDH(A4,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z4">
-        <f>IFERROR(BDH(A4,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA4">
-        <f>IFERROR(BDH(A4,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB4">
-        <f>IFERROR(BDH(A4,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC4">
-        <f>IFERROR(BDH(A4,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD4">
-        <f>IFERROR(BDH(A4,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE4">
-        <f>IFERROR(BDH(A4,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF4">
-        <f>IFERROR(BDH(A4,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG4">
-        <f>IFERROR(BDH(A4,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -82412,7 +82412,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="17">
-        <f>IFERROR(BDP(A5,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C5-AG5,"")</f>
         <v>0</v>
       </c>
       <c r="E5" s="18">
@@ -82448,83 +82448,83 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <f>IFERROR(BDH(A5,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O5">
-        <f>IFERROR(BDH(A5,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P5">
-        <f>IFERROR(BDH(A5,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q5">
-        <f>IFERROR(BDH(A5,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R5">
-        <f>IFERROR(BDH(A5,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S5">
-        <f>IFERROR(BDH(A5,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T5">
-        <f>IFERROR(BDH(A5,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U5">
-        <f>IFERROR(BDH(A5,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V5">
-        <f>IFERROR(BDH(A5,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W5">
-        <f>IFERROR(BDH(A5,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X5">
-        <f>IFERROR(BDH(A5,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y5">
-        <f>IFERROR(BDH(A5,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z5">
-        <f>IFERROR(BDH(A5,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA5">
-        <f>IFERROR(BDH(A5,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB5">
-        <f>IFERROR(BDH(A5,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC5">
-        <f>IFERROR(BDH(A5,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD5">
-        <f>IFERROR(BDH(A5,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE5">
-        <f>IFERROR(BDH(A5,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF5">
-        <f>IFERROR(BDH(A5,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG5">
-        <f>IFERROR(BDH(A5,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -82542,7 +82542,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="22">
-        <f>IFERROR(BDP(A6,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C6-AG6,"")</f>
         <v>0</v>
       </c>
       <c r="E6" s="23">
@@ -82578,83 +82578,83 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <f>IFERROR(BDH(A6,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O6">
-        <f>IFERROR(BDH(A6,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P6">
-        <f>IFERROR(BDH(A6,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q6">
-        <f>IFERROR(BDH(A6,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R6">
-        <f>IFERROR(BDH(A6,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S6">
-        <f>IFERROR(BDH(A6,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T6">
-        <f>IFERROR(BDH(A6,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U6">
-        <f>IFERROR(BDH(A6,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V6">
-        <f>IFERROR(BDH(A6,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W6">
-        <f>IFERROR(BDH(A6,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X6">
-        <f>IFERROR(BDH(A6,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y6">
-        <f>IFERROR(BDH(A6,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z6">
-        <f>IFERROR(BDH(A6,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA6">
-        <f>IFERROR(BDH(A6,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB6">
-        <f>IFERROR(BDH(A6,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC6">
-        <f>IFERROR(BDH(A6,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD6">
-        <f>IFERROR(BDH(A6,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE6">
-        <f>IFERROR(BDH(A6,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF6">
-        <f>IFERROR(BDH(A6,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG6">
-        <f>IFERROR(BDH(A6,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -82672,7 +82672,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="17">
-        <f>IFERROR(BDP(A7,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C7-AG7,"")</f>
         <v>0</v>
       </c>
       <c r="E7" s="18">
@@ -82708,83 +82708,83 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <f>IFERROR(BDH(A7,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O7">
-        <f>IFERROR(BDH(A7,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P7">
-        <f>IFERROR(BDH(A7,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q7">
-        <f>IFERROR(BDH(A7,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R7">
-        <f>IFERROR(BDH(A7,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S7">
-        <f>IFERROR(BDH(A7,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T7">
-        <f>IFERROR(BDH(A7,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U7">
-        <f>IFERROR(BDH(A7,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V7">
-        <f>IFERROR(BDH(A7,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W7">
-        <f>IFERROR(BDH(A7,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X7">
-        <f>IFERROR(BDH(A7,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y7">
-        <f>IFERROR(BDH(A7,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z7">
-        <f>IFERROR(BDH(A7,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA7">
-        <f>IFERROR(BDH(A7,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB7">
-        <f>IFERROR(BDH(A7,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC7">
-        <f>IFERROR(BDH(A7,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD7">
-        <f>IFERROR(BDH(A7,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE7">
-        <f>IFERROR(BDH(A7,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF7">
-        <f>IFERROR(BDH(A7,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG7">
-        <f>IFERROR(BDH(A7,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -82802,7 +82802,7 @@
         <v>0</v>
       </c>
       <c r="D8" s="22">
-        <f>IFERROR(BDP(A8,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C8-AG8,"")</f>
         <v>0</v>
       </c>
       <c r="E8" s="23">
@@ -82838,83 +82838,83 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <f>IFERROR(BDH(A8,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O8">
-        <f>IFERROR(BDH(A8,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P8">
-        <f>IFERROR(BDH(A8,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q8">
-        <f>IFERROR(BDH(A8,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R8">
-        <f>IFERROR(BDH(A8,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S8">
-        <f>IFERROR(BDH(A8,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T8">
-        <f>IFERROR(BDH(A8,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U8">
-        <f>IFERROR(BDH(A8,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V8">
-        <f>IFERROR(BDH(A8,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W8">
-        <f>IFERROR(BDH(A8,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X8">
-        <f>IFERROR(BDH(A8,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y8">
-        <f>IFERROR(BDH(A8,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z8">
-        <f>IFERROR(BDH(A8,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA8">
-        <f>IFERROR(BDH(A8,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB8">
-        <f>IFERROR(BDH(A8,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC8">
-        <f>IFERROR(BDH(A8,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD8">
-        <f>IFERROR(BDH(A8,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE8">
-        <f>IFERROR(BDH(A8,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF8">
-        <f>IFERROR(BDH(A8,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG8">
-        <f>IFERROR(BDH(A8,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -82932,7 +82932,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="17">
-        <f>IFERROR(BDP(A9,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C9-AG9,"")</f>
         <v>0</v>
       </c>
       <c r="E9" s="18">
@@ -82968,83 +82968,83 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <f>IFERROR(BDH(A9,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O9">
-        <f>IFERROR(BDH(A9,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P9">
-        <f>IFERROR(BDH(A9,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q9">
-        <f>IFERROR(BDH(A9,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R9">
-        <f>IFERROR(BDH(A9,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S9">
-        <f>IFERROR(BDH(A9,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T9">
-        <f>IFERROR(BDH(A9,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U9">
-        <f>IFERROR(BDH(A9,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V9">
-        <f>IFERROR(BDH(A9,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W9">
-        <f>IFERROR(BDH(A9,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X9">
-        <f>IFERROR(BDH(A9,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y9">
-        <f>IFERROR(BDH(A9,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z9">
-        <f>IFERROR(BDH(A9,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA9">
-        <f>IFERROR(BDH(A9,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB9">
-        <f>IFERROR(BDH(A9,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC9">
-        <f>IFERROR(BDH(A9,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD9">
-        <f>IFERROR(BDH(A9,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE9">
-        <f>IFERROR(BDH(A9,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF9">
-        <f>IFERROR(BDH(A9,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG9">
-        <f>IFERROR(BDH(A9,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -83062,7 +83062,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="22">
-        <f>IFERROR(BDP(A10,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C10-AG10,"")</f>
         <v>0</v>
       </c>
       <c r="E10" s="23">
@@ -83098,83 +83098,83 @@
         <v>0</v>
       </c>
       <c r="N10">
-        <f>IFERROR(BDH(A10,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O10">
-        <f>IFERROR(BDH(A10,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P10">
-        <f>IFERROR(BDH(A10,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q10">
-        <f>IFERROR(BDH(A10,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R10">
-        <f>IFERROR(BDH(A10,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S10">
-        <f>IFERROR(BDH(A10,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T10">
-        <f>IFERROR(BDH(A10,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U10">
-        <f>IFERROR(BDH(A10,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V10">
-        <f>IFERROR(BDH(A10,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W10">
-        <f>IFERROR(BDH(A10,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X10">
-        <f>IFERROR(BDH(A10,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y10">
-        <f>IFERROR(BDH(A10,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z10">
-        <f>IFERROR(BDH(A10,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA10">
-        <f>IFERROR(BDH(A10,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB10">
-        <f>IFERROR(BDH(A10,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC10">
-        <f>IFERROR(BDH(A10,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD10">
-        <f>IFERROR(BDH(A10,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE10">
-        <f>IFERROR(BDH(A10,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF10">
-        <f>IFERROR(BDH(A10,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG10">
-        <f>IFERROR(BDH(A10,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -83192,7 +83192,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="17">
-        <f>IFERROR(BDP(A11,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C11-AG11,"")</f>
         <v>0</v>
       </c>
       <c r="E11" s="18">
@@ -83228,83 +83228,83 @@
         <v>0</v>
       </c>
       <c r="N11">
-        <f>IFERROR(BDH(A11,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O11">
-        <f>IFERROR(BDH(A11,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P11">
-        <f>IFERROR(BDH(A11,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q11">
-        <f>IFERROR(BDH(A11,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R11">
-        <f>IFERROR(BDH(A11,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S11">
-        <f>IFERROR(BDH(A11,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T11">
-        <f>IFERROR(BDH(A11,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U11">
-        <f>IFERROR(BDH(A11,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V11">
-        <f>IFERROR(BDH(A11,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W11">
-        <f>IFERROR(BDH(A11,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X11">
-        <f>IFERROR(BDH(A11,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y11">
-        <f>IFERROR(BDH(A11,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z11">
-        <f>IFERROR(BDH(A11,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA11">
-        <f>IFERROR(BDH(A11,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB11">
-        <f>IFERROR(BDH(A11,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC11">
-        <f>IFERROR(BDH(A11,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD11">
-        <f>IFERROR(BDH(A11,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE11">
-        <f>IFERROR(BDH(A11,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF11">
-        <f>IFERROR(BDH(A11,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG11">
-        <f>IFERROR(BDH(A11,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -83322,7 +83322,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="22">
-        <f>IFERROR(BDP(A12,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C12-AG12,"")</f>
         <v>0</v>
       </c>
       <c r="E12" s="23">
@@ -83358,83 +83358,83 @@
         <v>0</v>
       </c>
       <c r="N12">
-        <f>IFERROR(BDH(A12,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O12">
-        <f>IFERROR(BDH(A12,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P12">
-        <f>IFERROR(BDH(A12,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q12">
-        <f>IFERROR(BDH(A12,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R12">
-        <f>IFERROR(BDH(A12,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S12">
-        <f>IFERROR(BDH(A12,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T12">
-        <f>IFERROR(BDH(A12,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U12">
-        <f>IFERROR(BDH(A12,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V12">
-        <f>IFERROR(BDH(A12,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W12">
-        <f>IFERROR(BDH(A12,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X12">
-        <f>IFERROR(BDH(A12,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y12">
-        <f>IFERROR(BDH(A12,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z12">
-        <f>IFERROR(BDH(A12,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA12">
-        <f>IFERROR(BDH(A12,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB12">
-        <f>IFERROR(BDH(A12,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC12">
-        <f>IFERROR(BDH(A12,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD12">
-        <f>IFERROR(BDH(A12,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE12">
-        <f>IFERROR(BDH(A12,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF12">
-        <f>IFERROR(BDH(A12,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG12">
-        <f>IFERROR(BDH(A12,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -83452,7 +83452,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="17">
-        <f>IFERROR(BDP(A13,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C13-AG13,"")</f>
         <v>0</v>
       </c>
       <c r="E13" s="18">
@@ -83488,83 +83488,83 @@
         <v>0</v>
       </c>
       <c r="N13">
-        <f>IFERROR(BDH(A13,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O13">
-        <f>IFERROR(BDH(A13,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P13">
-        <f>IFERROR(BDH(A13,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q13">
-        <f>IFERROR(BDH(A13,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R13">
-        <f>IFERROR(BDH(A13,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S13">
-        <f>IFERROR(BDH(A13,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T13">
-        <f>IFERROR(BDH(A13,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U13">
-        <f>IFERROR(BDH(A13,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V13">
-        <f>IFERROR(BDH(A13,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W13">
-        <f>IFERROR(BDH(A13,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X13">
-        <f>IFERROR(BDH(A13,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y13">
-        <f>IFERROR(BDH(A13,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z13">
-        <f>IFERROR(BDH(A13,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA13">
-        <f>IFERROR(BDH(A13,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB13">
-        <f>IFERROR(BDH(A13,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC13">
-        <f>IFERROR(BDH(A13,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD13">
-        <f>IFERROR(BDH(A13,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE13">
-        <f>IFERROR(BDH(A13,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF13">
-        <f>IFERROR(BDH(A13,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG13">
-        <f>IFERROR(BDH(A13,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A13,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -83582,7 +83582,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="22">
-        <f>IFERROR(BDP(A14,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C14-AG14,"")</f>
         <v>0</v>
       </c>
       <c r="E14" s="23">
@@ -83618,83 +83618,83 @@
         <v>0</v>
       </c>
       <c r="N14">
-        <f>IFERROR(BDH(A14,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O14">
-        <f>IFERROR(BDH(A14,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P14">
-        <f>IFERROR(BDH(A14,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q14">
-        <f>IFERROR(BDH(A14,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R14">
-        <f>IFERROR(BDH(A14,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S14">
-        <f>IFERROR(BDH(A14,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T14">
-        <f>IFERROR(BDH(A14,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U14">
-        <f>IFERROR(BDH(A14,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V14">
-        <f>IFERROR(BDH(A14,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W14">
-        <f>IFERROR(BDH(A14,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X14">
-        <f>IFERROR(BDH(A14,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y14">
-        <f>IFERROR(BDH(A14,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z14">
-        <f>IFERROR(BDH(A14,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA14">
-        <f>IFERROR(BDH(A14,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB14">
-        <f>IFERROR(BDH(A14,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC14">
-        <f>IFERROR(BDH(A14,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD14">
-        <f>IFERROR(BDH(A14,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE14">
-        <f>IFERROR(BDH(A14,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF14">
-        <f>IFERROR(BDH(A14,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG14">
-        <f>IFERROR(BDH(A14,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A14,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -83712,7 +83712,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="17">
-        <f>IFERROR(BDP(A15,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C15-AG15,"")</f>
         <v>0</v>
       </c>
       <c r="E15" s="18">
@@ -83748,83 +83748,83 @@
         <v>0</v>
       </c>
       <c r="N15">
-        <f>IFERROR(BDH(A15,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O15">
-        <f>IFERROR(BDH(A15,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P15">
-        <f>IFERROR(BDH(A15,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q15">
-        <f>IFERROR(BDH(A15,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R15">
-        <f>IFERROR(BDH(A15,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S15">
-        <f>IFERROR(BDH(A15,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T15">
-        <f>IFERROR(BDH(A15,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U15">
-        <f>IFERROR(BDH(A15,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V15">
-        <f>IFERROR(BDH(A15,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W15">
-        <f>IFERROR(BDH(A15,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X15">
-        <f>IFERROR(BDH(A15,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y15">
-        <f>IFERROR(BDH(A15,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z15">
-        <f>IFERROR(BDH(A15,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA15">
-        <f>IFERROR(BDH(A15,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB15">
-        <f>IFERROR(BDH(A15,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC15">
-        <f>IFERROR(BDH(A15,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD15">
-        <f>IFERROR(BDH(A15,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE15">
-        <f>IFERROR(BDH(A15,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF15">
-        <f>IFERROR(BDH(A15,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG15">
-        <f>IFERROR(BDH(A15,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A15,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -83842,7 +83842,7 @@
         <v>0</v>
       </c>
       <c r="D16" s="22">
-        <f>IFERROR(BDP(A16,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C16-AG16,"")</f>
         <v>0</v>
       </c>
       <c r="E16" s="23">
@@ -83878,83 +83878,83 @@
         <v>0</v>
       </c>
       <c r="N16">
-        <f>IFERROR(BDH(A16,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O16">
-        <f>IFERROR(BDH(A16,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P16">
-        <f>IFERROR(BDH(A16,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q16">
-        <f>IFERROR(BDH(A16,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R16">
-        <f>IFERROR(BDH(A16,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S16">
-        <f>IFERROR(BDH(A16,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T16">
-        <f>IFERROR(BDH(A16,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U16">
-        <f>IFERROR(BDH(A16,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V16">
-        <f>IFERROR(BDH(A16,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W16">
-        <f>IFERROR(BDH(A16,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X16">
-        <f>IFERROR(BDH(A16,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y16">
-        <f>IFERROR(BDH(A16,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z16">
-        <f>IFERROR(BDH(A16,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA16">
-        <f>IFERROR(BDH(A16,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB16">
-        <f>IFERROR(BDH(A16,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC16">
-        <f>IFERROR(BDH(A16,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD16">
-        <f>IFERROR(BDH(A16,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE16">
-        <f>IFERROR(BDH(A16,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF16">
-        <f>IFERROR(BDH(A16,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG16">
-        <f>IFERROR(BDH(A16,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A16,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>
@@ -83972,7 +83972,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="17">
-        <f>IFERROR(BDP(A17,"NET_CHNG_1D"),"")</f>
+        <f>IFERROR(C17-AG17,"")</f>
         <v>0</v>
       </c>
       <c r="E17" s="18">
@@ -84008,83 +84008,83 @@
         <v>0</v>
       </c>
       <c r="N17">
-        <f>IFERROR(BDH(A17,"PX_LAST",N$2,N$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
         <v>0</v>
       </c>
       <c r="O17">
-        <f>IFERROR(BDH(A17,"PX_LAST",O$2,O$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
         <v>0</v>
       </c>
       <c r="P17">
-        <f>IFERROR(BDH(A17,"PX_LAST",P$2,P$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
         <v>0</v>
       </c>
       <c r="Q17">
-        <f>IFERROR(BDH(A17,"PX_LAST",Q$2,Q$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
         <v>0</v>
       </c>
       <c r="R17">
-        <f>IFERROR(BDH(A17,"PX_LAST",R$2,R$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
         <v>0</v>
       </c>
       <c r="S17">
-        <f>IFERROR(BDH(A17,"PX_LAST",S$2,S$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
         <v>0</v>
       </c>
       <c r="T17">
-        <f>IFERROR(BDH(A17,"PX_LAST",T$2,T$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
         <v>0</v>
       </c>
       <c r="U17">
-        <f>IFERROR(BDH(A17,"PX_LAST",U$2,U$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
         <v>0</v>
       </c>
       <c r="V17">
-        <f>IFERROR(BDH(A17,"PX_LAST",V$2,V$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
         <v>0</v>
       </c>
       <c r="W17">
-        <f>IFERROR(BDH(A17,"PX_LAST",W$2,W$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
         <v>0</v>
       </c>
       <c r="X17">
-        <f>IFERROR(BDH(A17,"PX_LAST",X$2,X$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
         <v>0</v>
       </c>
       <c r="Y17">
-        <f>IFERROR(BDH(A17,"PX_LAST",Y$2,Y$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
         <v>0</v>
       </c>
       <c r="Z17">
-        <f>IFERROR(BDH(A17,"PX_LAST",Z$2,Z$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
         <v>0</v>
       </c>
       <c r="AA17">
-        <f>IFERROR(BDH(A17,"PX_LAST",AA$2,AA$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
         <v>0</v>
       </c>
       <c r="AB17">
-        <f>IFERROR(BDH(A17,"PX_LAST",AB$2,AB$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
         <v>0</v>
       </c>
       <c r="AC17">
-        <f>IFERROR(BDH(A17,"PX_LAST",AC$2,AC$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
         <v>0</v>
       </c>
       <c r="AD17">
-        <f>IFERROR(BDH(A17,"PX_LAST",AD$2,AD$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
         <v>0</v>
       </c>
       <c r="AE17">
-        <f>IFERROR(BDH(A17,"PX_LAST",AE$2,AE$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
         <v>0</v>
       </c>
       <c r="AF17">
-        <f>IFERROR(BDH(A17,"PX_LAST",AF$2,AF$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
         <v>0</v>
       </c>
       <c r="AG17">
-        <f>IFERROR(BDH(A17,"PX_LAST",AG$2,AG$2),"")</f>
+        <f>IFERROR(BDH(A17,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
         <v>0</v>
       </c>
     </row>

--- a/Workbook/Most.Traded.Universe.xlsx
+++ b/Workbook/Most.Traded.Universe.xlsx
@@ -44724,95 +44724,95 @@
         <v>0</v>
       </c>
       <c r="M3" s="21">
-        <f>IFERROR(IF(AND(H3&lt;0,J3&gt;0),"BUY",IF(AND(H3&gt;0,J3&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J3="",H3=""),"",IF(AND(H3&lt;0,J3&gt;0),"BUY",IF(AND(H3&gt;0,J3&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N3">
-        <f>IFERROR(AVERAGE(P3:AI3),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P3:AI3),"")</f>
         <v>0</v>
       </c>
       <c r="O3">
-        <f>IFERROR(STDEV(P3:AI3),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P3:AI3),"")</f>
         <v>0</v>
       </c>
       <c r="P3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -44862,95 +44862,95 @@
         <v>0</v>
       </c>
       <c r="M4" s="28">
-        <f>IFERROR(IF(AND(H4&lt;0,J4&gt;0),"BUY",IF(AND(H4&gt;0,J4&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J4="",H4=""),"",IF(AND(H4&lt;0,J4&gt;0),"BUY",IF(AND(H4&gt;0,J4&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N4">
-        <f>IFERROR(AVERAGE(P4:AI4),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P4:AI4),"")</f>
         <v>0</v>
       </c>
       <c r="O4">
-        <f>IFERROR(STDEV(P4:AI4),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P4:AI4),"")</f>
         <v>0</v>
       </c>
       <c r="P4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -45000,95 +45000,95 @@
         <v>0</v>
       </c>
       <c r="M5" s="21">
-        <f>IFERROR(IF(AND(H5&lt;0,J5&gt;0),"BUY",IF(AND(H5&gt;0,J5&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J5="",H5=""),"",IF(AND(H5&lt;0,J5&gt;0),"BUY",IF(AND(H5&gt;0,J5&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N5">
-        <f>IFERROR(AVERAGE(P5:AI5),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P5:AI5),"")</f>
         <v>0</v>
       </c>
       <c r="O5">
-        <f>IFERROR(STDEV(P5:AI5),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P5:AI5),"")</f>
         <v>0</v>
       </c>
       <c r="P5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -45138,95 +45138,95 @@
         <v>0</v>
       </c>
       <c r="M6" s="28">
-        <f>IFERROR(IF(AND(H6&lt;0,J6&gt;0),"BUY",IF(AND(H6&gt;0,J6&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J6="",H6=""),"",IF(AND(H6&lt;0,J6&gt;0),"BUY",IF(AND(H6&gt;0,J6&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N6">
-        <f>IFERROR(AVERAGE(P6:AI6),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P6:AI6),"")</f>
         <v>0</v>
       </c>
       <c r="O6">
-        <f>IFERROR(STDEV(P6:AI6),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P6:AI6),"")</f>
         <v>0</v>
       </c>
       <c r="P6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -45276,95 +45276,95 @@
         <v>0</v>
       </c>
       <c r="M7" s="21">
-        <f>IFERROR(IF(AND(H7&lt;0,J7&gt;0),"BUY",IF(AND(H7&gt;0,J7&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J7="",H7=""),"",IF(AND(H7&lt;0,J7&gt;0),"BUY",IF(AND(H7&gt;0,J7&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N7">
-        <f>IFERROR(AVERAGE(P7:AI7),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P7:AI7),"")</f>
         <v>0</v>
       </c>
       <c r="O7">
-        <f>IFERROR(STDEV(P7:AI7),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P7:AI7),"")</f>
         <v>0</v>
       </c>
       <c r="P7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -45414,95 +45414,95 @@
         <v>0</v>
       </c>
       <c r="M8" s="28">
-        <f>IFERROR(IF(AND(H8&lt;0,J8&gt;0),"BUY",IF(AND(H8&gt;0,J8&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J8="",H8=""),"",IF(AND(H8&lt;0,J8&gt;0),"BUY",IF(AND(H8&gt;0,J8&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N8">
-        <f>IFERROR(AVERAGE(P8:AI8),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P8:AI8),"")</f>
         <v>0</v>
       </c>
       <c r="O8">
-        <f>IFERROR(STDEV(P8:AI8),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P8:AI8),"")</f>
         <v>0</v>
       </c>
       <c r="P8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -45552,95 +45552,95 @@
         <v>0</v>
       </c>
       <c r="M9" s="21">
-        <f>IFERROR(IF(AND(H9&lt;0,J9&gt;0),"BUY",IF(AND(H9&gt;0,J9&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J9="",H9=""),"",IF(AND(H9&lt;0,J9&gt;0),"BUY",IF(AND(H9&gt;0,J9&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N9">
-        <f>IFERROR(AVERAGE(P9:AI9),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P9:AI9),"")</f>
         <v>0</v>
       </c>
       <c r="O9">
-        <f>IFERROR(STDEV(P9:AI9),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P9:AI9),"")</f>
         <v>0</v>
       </c>
       <c r="P9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -45690,95 +45690,95 @@
         <v>0</v>
       </c>
       <c r="M10" s="28">
-        <f>IFERROR(IF(AND(H10&lt;0,J10&gt;0),"BUY",IF(AND(H10&gt;0,J10&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J10="",H10=""),"",IF(AND(H10&lt;0,J10&gt;0),"BUY",IF(AND(H10&gt;0,J10&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N10">
-        <f>IFERROR(AVERAGE(P10:AI10),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P10:AI10),"")</f>
         <v>0</v>
       </c>
       <c r="O10">
-        <f>IFERROR(STDEV(P10:AI10),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P10:AI10),"")</f>
         <v>0</v>
       </c>
       <c r="P10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -45828,95 +45828,95 @@
         <v>0</v>
       </c>
       <c r="M11" s="21">
-        <f>IFERROR(IF(AND(H11&lt;0,J11&gt;0),"BUY",IF(AND(H11&gt;0,J11&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J11="",H11=""),"",IF(AND(H11&lt;0,J11&gt;0),"BUY",IF(AND(H11&gt;0,J11&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N11">
-        <f>IFERROR(AVERAGE(P11:AI11),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P11:AI11),"")</f>
         <v>0</v>
       </c>
       <c r="O11">
-        <f>IFERROR(STDEV(P11:AI11),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P11:AI11),"")</f>
         <v>0</v>
       </c>
       <c r="P11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -45966,95 +45966,95 @@
         <v>0</v>
       </c>
       <c r="M12" s="28">
-        <f>IFERROR(IF(AND(H12&lt;0,J12&gt;0),"BUY",IF(AND(H12&gt;0,J12&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J12="",H12=""),"",IF(AND(H12&lt;0,J12&gt;0),"BUY",IF(AND(H12&gt;0,J12&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N12">
-        <f>IFERROR(AVERAGE(P12:AI12),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P12:AI12),"")</f>
         <v>0</v>
       </c>
       <c r="O12">
-        <f>IFERROR(STDEV(P12:AI12),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P12:AI12),"")</f>
         <v>0</v>
       </c>
       <c r="P12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -46097,7 +46097,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{05C60535-1F16-4fd2-B633-F4F36F0B64E0}">
       <x14:sparklineGroups xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FFC00000"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -46113,7 +46113,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FFC00000"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -46129,7 +46129,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FFC00000"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -46145,7 +46145,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FFC00000"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -46161,7 +46161,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FFC00000"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -46177,7 +46177,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FFC00000"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -46193,7 +46193,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FFC00000"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -46209,7 +46209,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FFC00000"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -46225,7 +46225,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FFC00000"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -46241,7 +46241,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FFC00000"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -55521,95 +55521,95 @@
         <v>0</v>
       </c>
       <c r="M3" s="21">
-        <f>IFERROR(IF(AND(H3&lt;0,J3&gt;0),"BUY",IF(AND(H3&gt;0,J3&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J3="",H3=""),"",IF(AND(H3&lt;0,J3&gt;0),"BUY",IF(AND(H3&gt;0,J3&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N3">
-        <f>IFERROR(AVERAGE(P3:AI3),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P3:AI3),"")</f>
         <v>0</v>
       </c>
       <c r="O3">
-        <f>IFERROR(STDEV(P3:AI3),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P3:AI3),"")</f>
         <v>0</v>
       </c>
       <c r="P3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -55659,95 +55659,95 @@
         <v>0</v>
       </c>
       <c r="M4" s="28">
-        <f>IFERROR(IF(AND(H4&lt;0,J4&gt;0),"BUY",IF(AND(H4&gt;0,J4&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J4="",H4=""),"",IF(AND(H4&lt;0,J4&gt;0),"BUY",IF(AND(H4&gt;0,J4&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N4">
-        <f>IFERROR(AVERAGE(P4:AI4),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P4:AI4),"")</f>
         <v>0</v>
       </c>
       <c r="O4">
-        <f>IFERROR(STDEV(P4:AI4),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P4:AI4),"")</f>
         <v>0</v>
       </c>
       <c r="P4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -55797,95 +55797,95 @@
         <v>0</v>
       </c>
       <c r="M5" s="21">
-        <f>IFERROR(IF(AND(H5&lt;0,J5&gt;0),"BUY",IF(AND(H5&gt;0,J5&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J5="",H5=""),"",IF(AND(H5&lt;0,J5&gt;0),"BUY",IF(AND(H5&gt;0,J5&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N5">
-        <f>IFERROR(AVERAGE(P5:AI5),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P5:AI5),"")</f>
         <v>0</v>
       </c>
       <c r="O5">
-        <f>IFERROR(STDEV(P5:AI5),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P5:AI5),"")</f>
         <v>0</v>
       </c>
       <c r="P5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -55935,95 +55935,95 @@
         <v>0</v>
       </c>
       <c r="M6" s="28">
-        <f>IFERROR(IF(AND(H6&lt;0,J6&gt;0),"BUY",IF(AND(H6&gt;0,J6&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J6="",H6=""),"",IF(AND(H6&lt;0,J6&gt;0),"BUY",IF(AND(H6&gt;0,J6&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N6">
-        <f>IFERROR(AVERAGE(P6:AI6),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P6:AI6),"")</f>
         <v>0</v>
       </c>
       <c r="O6">
-        <f>IFERROR(STDEV(P6:AI6),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P6:AI6),"")</f>
         <v>0</v>
       </c>
       <c r="P6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -56073,95 +56073,95 @@
         <v>0</v>
       </c>
       <c r="M7" s="21">
-        <f>IFERROR(IF(AND(H7&lt;0,J7&gt;0),"BUY",IF(AND(H7&gt;0,J7&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J7="",H7=""),"",IF(AND(H7&lt;0,J7&gt;0),"BUY",IF(AND(H7&gt;0,J7&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N7">
-        <f>IFERROR(AVERAGE(P7:AI7),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P7:AI7),"")</f>
         <v>0</v>
       </c>
       <c r="O7">
-        <f>IFERROR(STDEV(P7:AI7),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P7:AI7),"")</f>
         <v>0</v>
       </c>
       <c r="P7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -56211,95 +56211,95 @@
         <v>0</v>
       </c>
       <c r="M8" s="28">
-        <f>IFERROR(IF(AND(H8&lt;0,J8&gt;0),"BUY",IF(AND(H8&gt;0,J8&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J8="",H8=""),"",IF(AND(H8&lt;0,J8&gt;0),"BUY",IF(AND(H8&gt;0,J8&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N8">
-        <f>IFERROR(AVERAGE(P8:AI8),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P8:AI8),"")</f>
         <v>0</v>
       </c>
       <c r="O8">
-        <f>IFERROR(STDEV(P8:AI8),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P8:AI8),"")</f>
         <v>0</v>
       </c>
       <c r="P8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -56349,95 +56349,95 @@
         <v>0</v>
       </c>
       <c r="M9" s="21">
-        <f>IFERROR(IF(AND(H9&lt;0,J9&gt;0),"BUY",IF(AND(H9&gt;0,J9&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J9="",H9=""),"",IF(AND(H9&lt;0,J9&gt;0),"BUY",IF(AND(H9&gt;0,J9&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N9">
-        <f>IFERROR(AVERAGE(P9:AI9),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P9:AI9),"")</f>
         <v>0</v>
       </c>
       <c r="O9">
-        <f>IFERROR(STDEV(P9:AI9),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P9:AI9),"")</f>
         <v>0</v>
       </c>
       <c r="P9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -56487,95 +56487,95 @@
         <v>0</v>
       </c>
       <c r="M10" s="28">
-        <f>IFERROR(IF(AND(H10&lt;0,J10&gt;0),"BUY",IF(AND(H10&gt;0,J10&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J10="",H10=""),"",IF(AND(H10&lt;0,J10&gt;0),"BUY",IF(AND(H10&gt;0,J10&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N10">
-        <f>IFERROR(AVERAGE(P10:AI10),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P10:AI10),"")</f>
         <v>0</v>
       </c>
       <c r="O10">
-        <f>IFERROR(STDEV(P10:AI10),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P10:AI10),"")</f>
         <v>0</v>
       </c>
       <c r="P10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -56625,95 +56625,95 @@
         <v>0</v>
       </c>
       <c r="M11" s="21">
-        <f>IFERROR(IF(AND(H11&lt;0,J11&gt;0),"BUY",IF(AND(H11&gt;0,J11&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J11="",H11=""),"",IF(AND(H11&lt;0,J11&gt;0),"BUY",IF(AND(H11&gt;0,J11&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N11">
-        <f>IFERROR(AVERAGE(P11:AI11),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P11:AI11),"")</f>
         <v>0</v>
       </c>
       <c r="O11">
-        <f>IFERROR(STDEV(P11:AI11),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P11:AI11),"")</f>
         <v>0</v>
       </c>
       <c r="P11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -56763,95 +56763,95 @@
         <v>0</v>
       </c>
       <c r="M12" s="28">
-        <f>IFERROR(IF(AND(H12&lt;0,J12&gt;0),"BUY",IF(AND(H12&gt;0,J12&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J12="",H12=""),"",IF(AND(H12&lt;0,J12&gt;0),"BUY",IF(AND(H12&gt;0,J12&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N12">
-        <f>IFERROR(AVERAGE(P12:AI12),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P12:AI12),"")</f>
         <v>0</v>
       </c>
       <c r="O12">
-        <f>IFERROR(STDEV(P12:AI12),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P12:AI12),"")</f>
         <v>0</v>
       </c>
       <c r="P12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -56894,7 +56894,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{05C60535-1F16-4fd2-B633-F4F36F0B64E0}">
       <x14:sparklineGroups xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FF1F497D"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -56910,7 +56910,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FF1F497D"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -56926,7 +56926,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FF1F497D"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -56942,7 +56942,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FF1F497D"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -56958,7 +56958,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FF1F497D"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -56974,7 +56974,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FF1F497D"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -56990,7 +56990,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FF1F497D"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -57006,7 +57006,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FF1F497D"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -57022,7 +57022,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FF1F497D"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -57038,7 +57038,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FF1F497D"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -64521,95 +64521,95 @@
         <v>0</v>
       </c>
       <c r="M3" s="21">
-        <f>IFERROR(IF(AND(H3&lt;0,J3&gt;0),"BUY",IF(AND(H3&gt;0,J3&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J3="",H3=""),"",IF(AND(H3&lt;0,J3&gt;0),"BUY",IF(AND(H3&gt;0,J3&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N3">
-        <f>IFERROR(AVERAGE(P3:AI3),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P3:AI3),"")</f>
         <v>0</v>
       </c>
       <c r="O3">
-        <f>IFERROR(STDEV(P3:AI3),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P3:AI3),"")</f>
         <v>0</v>
       </c>
       <c r="P3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -64659,95 +64659,95 @@
         <v>0</v>
       </c>
       <c r="M4" s="28">
-        <f>IFERROR(IF(AND(H4&lt;0,J4&gt;0),"BUY",IF(AND(H4&gt;0,J4&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J4="",H4=""),"",IF(AND(H4&lt;0,J4&gt;0),"BUY",IF(AND(H4&gt;0,J4&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N4">
-        <f>IFERROR(AVERAGE(P4:AI4),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P4:AI4),"")</f>
         <v>0</v>
       </c>
       <c r="O4">
-        <f>IFERROR(STDEV(P4:AI4),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P4:AI4),"")</f>
         <v>0</v>
       </c>
       <c r="P4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -64797,95 +64797,95 @@
         <v>0</v>
       </c>
       <c r="M5" s="21">
-        <f>IFERROR(IF(AND(H5&lt;0,J5&gt;0),"BUY",IF(AND(H5&gt;0,J5&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J5="",H5=""),"",IF(AND(H5&lt;0,J5&gt;0),"BUY",IF(AND(H5&gt;0,J5&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N5">
-        <f>IFERROR(AVERAGE(P5:AI5),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P5:AI5),"")</f>
         <v>0</v>
       </c>
       <c r="O5">
-        <f>IFERROR(STDEV(P5:AI5),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P5:AI5),"")</f>
         <v>0</v>
       </c>
       <c r="P5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -64935,95 +64935,95 @@
         <v>0</v>
       </c>
       <c r="M6" s="28">
-        <f>IFERROR(IF(AND(H6&lt;0,J6&gt;0),"BUY",IF(AND(H6&gt;0,J6&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J6="",H6=""),"",IF(AND(H6&lt;0,J6&gt;0),"BUY",IF(AND(H6&gt;0,J6&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N6">
-        <f>IFERROR(AVERAGE(P6:AI6),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P6:AI6),"")</f>
         <v>0</v>
       </c>
       <c r="O6">
-        <f>IFERROR(STDEV(P6:AI6),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P6:AI6),"")</f>
         <v>0</v>
       </c>
       <c r="P6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -65073,95 +65073,95 @@
         <v>0</v>
       </c>
       <c r="M7" s="21">
-        <f>IFERROR(IF(AND(H7&lt;0,J7&gt;0),"BUY",IF(AND(H7&gt;0,J7&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J7="",H7=""),"",IF(AND(H7&lt;0,J7&gt;0),"BUY",IF(AND(H7&gt;0,J7&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N7">
-        <f>IFERROR(AVERAGE(P7:AI7),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P7:AI7),"")</f>
         <v>0</v>
       </c>
       <c r="O7">
-        <f>IFERROR(STDEV(P7:AI7),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P7:AI7),"")</f>
         <v>0</v>
       </c>
       <c r="P7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -65211,95 +65211,95 @@
         <v>0</v>
       </c>
       <c r="M8" s="28">
-        <f>IFERROR(IF(AND(H8&lt;0,J8&gt;0),"BUY",IF(AND(H8&gt;0,J8&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J8="",H8=""),"",IF(AND(H8&lt;0,J8&gt;0),"BUY",IF(AND(H8&gt;0,J8&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N8">
-        <f>IFERROR(AVERAGE(P8:AI8),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P8:AI8),"")</f>
         <v>0</v>
       </c>
       <c r="O8">
-        <f>IFERROR(STDEV(P8:AI8),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P8:AI8),"")</f>
         <v>0</v>
       </c>
       <c r="P8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -65349,95 +65349,95 @@
         <v>0</v>
       </c>
       <c r="M9" s="21">
-        <f>IFERROR(IF(AND(H9&lt;0,J9&gt;0),"BUY",IF(AND(H9&gt;0,J9&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J9="",H9=""),"",IF(AND(H9&lt;0,J9&gt;0),"BUY",IF(AND(H9&gt;0,J9&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N9">
-        <f>IFERROR(AVERAGE(P9:AI9),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P9:AI9),"")</f>
         <v>0</v>
       </c>
       <c r="O9">
-        <f>IFERROR(STDEV(P9:AI9),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P9:AI9),"")</f>
         <v>0</v>
       </c>
       <c r="P9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -65487,95 +65487,95 @@
         <v>0</v>
       </c>
       <c r="M10" s="28">
-        <f>IFERROR(IF(AND(H10&lt;0,J10&gt;0),"BUY",IF(AND(H10&gt;0,J10&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J10="",H10=""),"",IF(AND(H10&lt;0,J10&gt;0),"BUY",IF(AND(H10&gt;0,J10&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N10">
-        <f>IFERROR(AVERAGE(P10:AI10),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P10:AI10),"")</f>
         <v>0</v>
       </c>
       <c r="O10">
-        <f>IFERROR(STDEV(P10:AI10),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P10:AI10),"")</f>
         <v>0</v>
       </c>
       <c r="P10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -65625,95 +65625,95 @@
         <v>0</v>
       </c>
       <c r="M11" s="21">
-        <f>IFERROR(IF(AND(H11&lt;0,J11&gt;0),"BUY",IF(AND(H11&gt;0,J11&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J11="",H11=""),"",IF(AND(H11&lt;0,J11&gt;0),"BUY",IF(AND(H11&gt;0,J11&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N11">
-        <f>IFERROR(AVERAGE(P11:AI11),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P11:AI11),"")</f>
         <v>0</v>
       </c>
       <c r="O11">
-        <f>IFERROR(STDEV(P11:AI11),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P11:AI11),"")</f>
         <v>0</v>
       </c>
       <c r="P11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -65763,95 +65763,95 @@
         <v>0</v>
       </c>
       <c r="M12" s="28">
-        <f>IFERROR(IF(AND(H12&lt;0,J12&gt;0),"BUY",IF(AND(H12&gt;0,J12&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J12="",H12=""),"",IF(AND(H12&lt;0,J12&gt;0),"BUY",IF(AND(H12&gt;0,J12&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N12">
-        <f>IFERROR(AVERAGE(P12:AI12),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P12:AI12),"")</f>
         <v>0</v>
       </c>
       <c r="O12">
-        <f>IFERROR(STDEV(P12:AI12),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P12:AI12),"")</f>
         <v>0</v>
       </c>
       <c r="P12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -65894,7 +65894,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{05C60535-1F16-4fd2-B633-F4F36F0B64E0}">
       <x14:sparklineGroups xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FF974706"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -65910,7 +65910,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FF974706"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -65926,7 +65926,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FF974706"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -65942,7 +65942,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FF974706"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -65958,7 +65958,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FF974706"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -65974,7 +65974,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FF974706"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -65990,7 +65990,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FF974706"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -66006,7 +66006,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FF974706"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -66022,7 +66022,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FF974706"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -66038,7 +66038,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FF974706"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -72433,95 +72433,95 @@
         <v>0</v>
       </c>
       <c r="M3" s="21">
-        <f>IFERROR(IF(AND(H3&lt;0,J3&gt;0),"BUY",IF(AND(H3&gt;0,J3&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J3="",H3=""),"",IF(AND(H3&lt;0,J3&gt;0),"BUY",IF(AND(H3&gt;0,J3&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N3">
-        <f>IFERROR(AVERAGE(P3:AI3),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P3:AI3),"")</f>
         <v>0</v>
       </c>
       <c r="O3">
-        <f>IFERROR(STDEV(P3:AI3),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P3:AI3),"")</f>
         <v>0</v>
       </c>
       <c r="P3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -72571,95 +72571,95 @@
         <v>0</v>
       </c>
       <c r="M4" s="28">
-        <f>IFERROR(IF(AND(H4&lt;0,J4&gt;0),"BUY",IF(AND(H4&gt;0,J4&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J4="",H4=""),"",IF(AND(H4&lt;0,J4&gt;0),"BUY",IF(AND(H4&gt;0,J4&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N4">
-        <f>IFERROR(AVERAGE(P4:AI4),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P4:AI4),"")</f>
         <v>0</v>
       </c>
       <c r="O4">
-        <f>IFERROR(STDEV(P4:AI4),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P4:AI4),"")</f>
         <v>0</v>
       </c>
       <c r="P4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -72709,95 +72709,95 @@
         <v>0</v>
       </c>
       <c r="M5" s="21">
-        <f>IFERROR(IF(AND(H5&lt;0,J5&gt;0),"BUY",IF(AND(H5&gt;0,J5&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J5="",H5=""),"",IF(AND(H5&lt;0,J5&gt;0),"BUY",IF(AND(H5&gt;0,J5&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N5">
-        <f>IFERROR(AVERAGE(P5:AI5),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P5:AI5),"")</f>
         <v>0</v>
       </c>
       <c r="O5">
-        <f>IFERROR(STDEV(P5:AI5),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P5:AI5),"")</f>
         <v>0</v>
       </c>
       <c r="P5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -72847,95 +72847,95 @@
         <v>0</v>
       </c>
       <c r="M6" s="28">
-        <f>IFERROR(IF(AND(H6&lt;0,J6&gt;0),"BUY",IF(AND(H6&gt;0,J6&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J6="",H6=""),"",IF(AND(H6&lt;0,J6&gt;0),"BUY",IF(AND(H6&gt;0,J6&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N6">
-        <f>IFERROR(AVERAGE(P6:AI6),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P6:AI6),"")</f>
         <v>0</v>
       </c>
       <c r="O6">
-        <f>IFERROR(STDEV(P6:AI6),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P6:AI6),"")</f>
         <v>0</v>
       </c>
       <c r="P6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -72985,95 +72985,95 @@
         <v>0</v>
       </c>
       <c r="M7" s="21">
-        <f>IFERROR(IF(AND(H7&lt;0,J7&gt;0),"BUY",IF(AND(H7&gt;0,J7&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J7="",H7=""),"",IF(AND(H7&lt;0,J7&gt;0),"BUY",IF(AND(H7&gt;0,J7&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N7">
-        <f>IFERROR(AVERAGE(P7:AI7),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P7:AI7),"")</f>
         <v>0</v>
       </c>
       <c r="O7">
-        <f>IFERROR(STDEV(P7:AI7),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P7:AI7),"")</f>
         <v>0</v>
       </c>
       <c r="P7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -73123,95 +73123,95 @@
         <v>0</v>
       </c>
       <c r="M8" s="28">
-        <f>IFERROR(IF(AND(H8&lt;0,J8&gt;0),"BUY",IF(AND(H8&gt;0,J8&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J8="",H8=""),"",IF(AND(H8&lt;0,J8&gt;0),"BUY",IF(AND(H8&gt;0,J8&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N8">
-        <f>IFERROR(AVERAGE(P8:AI8),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P8:AI8),"")</f>
         <v>0</v>
       </c>
       <c r="O8">
-        <f>IFERROR(STDEV(P8:AI8),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P8:AI8),"")</f>
         <v>0</v>
       </c>
       <c r="P8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -73261,95 +73261,95 @@
         <v>0</v>
       </c>
       <c r="M9" s="21">
-        <f>IFERROR(IF(AND(H9&lt;0,J9&gt;0),"BUY",IF(AND(H9&gt;0,J9&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J9="",H9=""),"",IF(AND(H9&lt;0,J9&gt;0),"BUY",IF(AND(H9&gt;0,J9&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N9">
-        <f>IFERROR(AVERAGE(P9:AI9),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P9:AI9),"")</f>
         <v>0</v>
       </c>
       <c r="O9">
-        <f>IFERROR(STDEV(P9:AI9),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P9:AI9),"")</f>
         <v>0</v>
       </c>
       <c r="P9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -73399,95 +73399,95 @@
         <v>0</v>
       </c>
       <c r="M10" s="28">
-        <f>IFERROR(IF(AND(H10&lt;0,J10&gt;0),"BUY",IF(AND(H10&gt;0,J10&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J10="",H10=""),"",IF(AND(H10&lt;0,J10&gt;0),"BUY",IF(AND(H10&gt;0,J10&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N10">
-        <f>IFERROR(AVERAGE(P10:AI10),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P10:AI10),"")</f>
         <v>0</v>
       </c>
       <c r="O10">
-        <f>IFERROR(STDEV(P10:AI10),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P10:AI10),"")</f>
         <v>0</v>
       </c>
       <c r="P10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -73537,95 +73537,95 @@
         <v>0</v>
       </c>
       <c r="M11" s="21">
-        <f>IFERROR(IF(AND(H11&lt;0,J11&gt;0),"BUY",IF(AND(H11&gt;0,J11&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J11="",H11=""),"",IF(AND(H11&lt;0,J11&gt;0),"BUY",IF(AND(H11&gt;0,J11&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N11">
-        <f>IFERROR(AVERAGE(P11:AI11),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P11:AI11),"")</f>
         <v>0</v>
       </c>
       <c r="O11">
-        <f>IFERROR(STDEV(P11:AI11),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P11:AI11),"")</f>
         <v>0</v>
       </c>
       <c r="P11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -73675,95 +73675,95 @@
         <v>0</v>
       </c>
       <c r="M12" s="28">
-        <f>IFERROR(IF(AND(H12&lt;0,J12&gt;0),"BUY",IF(AND(H12&gt;0,J12&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J12="",H12=""),"",IF(AND(H12&lt;0,J12&gt;0),"BUY",IF(AND(H12&gt;0,J12&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N12">
-        <f>IFERROR(AVERAGE(P12:AI12),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P12:AI12),"")</f>
         <v>0</v>
       </c>
       <c r="O12">
-        <f>IFERROR(STDEV(P12:AI12),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P12:AI12),"")</f>
         <v>0</v>
       </c>
       <c r="P12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -73806,7 +73806,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{05C60535-1F16-4fd2-B633-F4F36F0B64E0}">
       <x14:sparklineGroups xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FF375623"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -73822,7 +73822,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FF375623"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -73838,7 +73838,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FF375623"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -73854,7 +73854,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FF375623"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -73870,7 +73870,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FF375623"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -73886,7 +73886,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FF375623"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -73902,7 +73902,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FF375623"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -73918,7 +73918,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FF375623"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -73934,7 +73934,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FF375623"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -73950,7 +73950,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FF375623"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -79801,95 +79801,95 @@
         <v>0</v>
       </c>
       <c r="M3" s="21">
-        <f>IFERROR(IF(AND(H3&lt;0,J3&gt;0),"BUY",IF(AND(H3&gt;0,J3&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J3="",H3=""),"",IF(AND(H3&lt;0,J3&gt;0),"BUY",IF(AND(H3&gt;0,J3&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N3">
-        <f>IFERROR(AVERAGE(P3:AI3),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P3:AI3),"")</f>
         <v>0</v>
       </c>
       <c r="O3">
-        <f>IFERROR(STDEV(P3:AI3),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P3:AI3),"")</f>
         <v>0</v>
       </c>
       <c r="P3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI3">
-        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A3,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -79939,95 +79939,95 @@
         <v>0</v>
       </c>
       <c r="M4" s="28">
-        <f>IFERROR(IF(AND(H4&lt;0,J4&gt;0),"BUY",IF(AND(H4&gt;0,J4&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J4="",H4=""),"",IF(AND(H4&lt;0,J4&gt;0),"BUY",IF(AND(H4&gt;0,J4&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N4">
-        <f>IFERROR(AVERAGE(P4:AI4),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P4:AI4),"")</f>
         <v>0</v>
       </c>
       <c r="O4">
-        <f>IFERROR(STDEV(P4:AI4),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P4:AI4),"")</f>
         <v>0</v>
       </c>
       <c r="P4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI4">
-        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A4,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -80077,95 +80077,95 @@
         <v>0</v>
       </c>
       <c r="M5" s="21">
-        <f>IFERROR(IF(AND(H5&lt;0,J5&gt;0),"BUY",IF(AND(H5&gt;0,J5&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J5="",H5=""),"",IF(AND(H5&lt;0,J5&gt;0),"BUY",IF(AND(H5&gt;0,J5&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N5">
-        <f>IFERROR(AVERAGE(P5:AI5),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P5:AI5),"")</f>
         <v>0</v>
       </c>
       <c r="O5">
-        <f>IFERROR(STDEV(P5:AI5),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P5:AI5),"")</f>
         <v>0</v>
       </c>
       <c r="P5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI5">
-        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A5,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -80215,95 +80215,95 @@
         <v>0</v>
       </c>
       <c r="M6" s="28">
-        <f>IFERROR(IF(AND(H6&lt;0,J6&gt;0),"BUY",IF(AND(H6&gt;0,J6&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J6="",H6=""),"",IF(AND(H6&lt;0,J6&gt;0),"BUY",IF(AND(H6&gt;0,J6&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N6">
-        <f>IFERROR(AVERAGE(P6:AI6),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P6:AI6),"")</f>
         <v>0</v>
       </c>
       <c r="O6">
-        <f>IFERROR(STDEV(P6:AI6),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P6:AI6),"")</f>
         <v>0</v>
       </c>
       <c r="P6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI6">
-        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A6,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -80353,95 +80353,95 @@
         <v>0</v>
       </c>
       <c r="M7" s="21">
-        <f>IFERROR(IF(AND(H7&lt;0,J7&gt;0),"BUY",IF(AND(H7&gt;0,J7&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J7="",H7=""),"",IF(AND(H7&lt;0,J7&gt;0),"BUY",IF(AND(H7&gt;0,J7&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N7">
-        <f>IFERROR(AVERAGE(P7:AI7),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P7:AI7),"")</f>
         <v>0</v>
       </c>
       <c r="O7">
-        <f>IFERROR(STDEV(P7:AI7),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P7:AI7),"")</f>
         <v>0</v>
       </c>
       <c r="P7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI7">
-        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A7,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -80491,95 +80491,95 @@
         <v>0</v>
       </c>
       <c r="M8" s="28">
-        <f>IFERROR(IF(AND(H8&lt;0,J8&gt;0),"BUY",IF(AND(H8&gt;0,J8&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J8="",H8=""),"",IF(AND(H8&lt;0,J8&gt;0),"BUY",IF(AND(H8&gt;0,J8&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N8">
-        <f>IFERROR(AVERAGE(P8:AI8),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P8:AI8),"")</f>
         <v>0</v>
       </c>
       <c r="O8">
-        <f>IFERROR(STDEV(P8:AI8),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P8:AI8),"")</f>
         <v>0</v>
       </c>
       <c r="P8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI8">
-        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A8,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -80629,95 +80629,95 @@
         <v>0</v>
       </c>
       <c r="M9" s="21">
-        <f>IFERROR(IF(AND(H9&lt;0,J9&gt;0),"BUY",IF(AND(H9&gt;0,J9&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J9="",H9=""),"",IF(AND(H9&lt;0,J9&gt;0),"BUY",IF(AND(H9&gt;0,J9&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N9">
-        <f>IFERROR(AVERAGE(P9:AI9),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P9:AI9),"")</f>
         <v>0</v>
       </c>
       <c r="O9">
-        <f>IFERROR(STDEV(P9:AI9),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P9:AI9),"")</f>
         <v>0</v>
       </c>
       <c r="P9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI9">
-        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A9,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -80767,95 +80767,95 @@
         <v>0</v>
       </c>
       <c r="M10" s="28">
-        <f>IFERROR(IF(AND(H10&lt;0,J10&gt;0),"BUY",IF(AND(H10&gt;0,J10&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J10="",H10=""),"",IF(AND(H10&lt;0,J10&gt;0),"BUY",IF(AND(H10&gt;0,J10&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N10">
-        <f>IFERROR(AVERAGE(P10:AI10),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P10:AI10),"")</f>
         <v>0</v>
       </c>
       <c r="O10">
-        <f>IFERROR(STDEV(P10:AI10),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P10:AI10),"")</f>
         <v>0</v>
       </c>
       <c r="P10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI10">
-        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A10,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -80905,95 +80905,95 @@
         <v>0</v>
       </c>
       <c r="M11" s="21">
-        <f>IFERROR(IF(AND(H11&lt;0,J11&gt;0),"BUY",IF(AND(H11&gt;0,J11&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J11="",H11=""),"",IF(AND(H11&lt;0,J11&gt;0),"BUY",IF(AND(H11&gt;0,J11&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N11">
-        <f>IFERROR(AVERAGE(P11:AI11),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P11:AI11),"")</f>
         <v>0</v>
       </c>
       <c r="O11">
-        <f>IFERROR(STDEV(P11:AI11),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P11:AI11),"")</f>
         <v>0</v>
       </c>
       <c r="P11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI11">
-        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A11,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -81043,95 +81043,95 @@
         <v>0</v>
       </c>
       <c r="M12" s="28">
-        <f>IFERROR(IF(AND(H12&lt;0,J12&gt;0),"BUY",IF(AND(H12&gt;0,J12&lt;0),"SELL","")),"")</f>
+        <f>IF(OR(J12="",H12=""),"",IF(AND(H12&lt;0,J12&gt;0),"BUY",IF(AND(H12&gt;0,J12&lt;0),"SELL","")))</f>
         <v>0</v>
       </c>
       <c r="N12">
-        <f>IFERROR(AVERAGE(P12:AI12),"")</f>
+        <f>IFERROR(AGGREGATE(1,6,P12:AI12),"")</f>
         <v>0</v>
       </c>
       <c r="O12">
-        <f>IFERROR(STDEV(P12:AI12),"")</f>
+        <f>IFERROR(AGGREGATE(8,6,P12:AI12),"")</f>
         <v>0</v>
       </c>
       <c r="P12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-20),WORKDAY(TODAY(),-20))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Q12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-19),WORKDAY(TODAY(),-19))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="R12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-18),WORKDAY(TODAY(),-18))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="S12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-17),WORKDAY(TODAY(),-17))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="T12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-16),WORKDAY(TODAY(),-16))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="U12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-15),WORKDAY(TODAY(),-15))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="V12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-14),WORKDAY(TODAY(),-14))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="W12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-13),WORKDAY(TODAY(),-13))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="X12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-12),WORKDAY(TODAY(),-12))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Y12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-11),WORKDAY(TODAY(),-11))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="Z12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-10),WORKDAY(TODAY(),-10))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AA12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-9),WORKDAY(TODAY(),-9))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AB12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-8),WORKDAY(TODAY(),-8))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AC12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-7),WORKDAY(TODAY(),-7))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AD12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-6),WORKDAY(TODAY(),-6))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AE12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-5),WORKDAY(TODAY(),-5))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AF12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-4),WORKDAY(TODAY(),-4))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AG12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-3),WORKDAY(TODAY(),-3))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AH12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-2),WORKDAY(TODAY(),-2))+0,NA())</f>
         <v>0</v>
       </c>
       <c r="AI12">
-        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1)),"")</f>
+        <f>IFERROR(BDH(A12,"PX_LAST",WORKDAY(TODAY(),-1),WORKDAY(TODAY(),-1))+0,NA())</f>
         <v>0</v>
       </c>
     </row>
@@ -81174,7 +81174,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{05C60535-1F16-4fd2-B633-F4F36F0B64E0}">
       <x14:sparklineGroups xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FF5B0A9F"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -81190,7 +81190,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FF5B0A9F"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -81206,7 +81206,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FF5B0A9F"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -81222,7 +81222,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FF5B0A9F"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -81238,7 +81238,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FF5B0A9F"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -81254,7 +81254,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FF5B0A9F"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -81270,7 +81270,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FF5B0A9F"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -81286,7 +81286,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FF5B0A9F"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -81302,7 +81302,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FF5B0A9F"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -81318,7 +81318,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" high="1" low="1">
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="span" high="1" low="1">
           <x14:colorSeries rgb="FF5B0A9F"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>

--- a/Workbook/Most.Traded.Universe.xlsx
+++ b/Workbook/Most.Traded.Universe.xlsx
@@ -44728,11 +44728,11 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <f>IFERROR(AGGREGATE(1,6,P3:AI3),"")</f>
+        <f t="array" ref="N3">IFERROR(AVERAGE(IF(ISNUMBER(P3:AI3),P3:AI3)),"")</f>
         <v>0</v>
       </c>
       <c r="O3">
-        <f>IFERROR(AGGREGATE(8,6,P3:AI3),"")</f>
+        <f t="array" ref="O3">IFERROR(STDEV(IF(ISNUMBER(P3:AI3),P3:AI3)),"")</f>
         <v>0</v>
       </c>
       <c r="P3">
@@ -44866,11 +44866,11 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <f>IFERROR(AGGREGATE(1,6,P4:AI4),"")</f>
+        <f t="array" ref="N4">IFERROR(AVERAGE(IF(ISNUMBER(P4:AI4),P4:AI4)),"")</f>
         <v>0</v>
       </c>
       <c r="O4">
-        <f>IFERROR(AGGREGATE(8,6,P4:AI4),"")</f>
+        <f t="array" ref="O4">IFERROR(STDEV(IF(ISNUMBER(P4:AI4),P4:AI4)),"")</f>
         <v>0</v>
       </c>
       <c r="P4">
@@ -45004,11 +45004,11 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <f>IFERROR(AGGREGATE(1,6,P5:AI5),"")</f>
+        <f t="array" ref="N5">IFERROR(AVERAGE(IF(ISNUMBER(P5:AI5),P5:AI5)),"")</f>
         <v>0</v>
       </c>
       <c r="O5">
-        <f>IFERROR(AGGREGATE(8,6,P5:AI5),"")</f>
+        <f t="array" ref="O5">IFERROR(STDEV(IF(ISNUMBER(P5:AI5),P5:AI5)),"")</f>
         <v>0</v>
       </c>
       <c r="P5">
@@ -45142,11 +45142,11 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <f>IFERROR(AGGREGATE(1,6,P6:AI6),"")</f>
+        <f t="array" ref="N6">IFERROR(AVERAGE(IF(ISNUMBER(P6:AI6),P6:AI6)),"")</f>
         <v>0</v>
       </c>
       <c r="O6">
-        <f>IFERROR(AGGREGATE(8,6,P6:AI6),"")</f>
+        <f t="array" ref="O6">IFERROR(STDEV(IF(ISNUMBER(P6:AI6),P6:AI6)),"")</f>
         <v>0</v>
       </c>
       <c r="P6">
@@ -45280,11 +45280,11 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <f>IFERROR(AGGREGATE(1,6,P7:AI7),"")</f>
+        <f t="array" ref="N7">IFERROR(AVERAGE(IF(ISNUMBER(P7:AI7),P7:AI7)),"")</f>
         <v>0</v>
       </c>
       <c r="O7">
-        <f>IFERROR(AGGREGATE(8,6,P7:AI7),"")</f>
+        <f t="array" ref="O7">IFERROR(STDEV(IF(ISNUMBER(P7:AI7),P7:AI7)),"")</f>
         <v>0</v>
       </c>
       <c r="P7">
@@ -45418,11 +45418,11 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <f>IFERROR(AGGREGATE(1,6,P8:AI8),"")</f>
+        <f t="array" ref="N8">IFERROR(AVERAGE(IF(ISNUMBER(P8:AI8),P8:AI8)),"")</f>
         <v>0</v>
       </c>
       <c r="O8">
-        <f>IFERROR(AGGREGATE(8,6,P8:AI8),"")</f>
+        <f t="array" ref="O8">IFERROR(STDEV(IF(ISNUMBER(P8:AI8),P8:AI8)),"")</f>
         <v>0</v>
       </c>
       <c r="P8">
@@ -45556,11 +45556,11 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <f>IFERROR(AGGREGATE(1,6,P9:AI9),"")</f>
+        <f t="array" ref="N9">IFERROR(AVERAGE(IF(ISNUMBER(P9:AI9),P9:AI9)),"")</f>
         <v>0</v>
       </c>
       <c r="O9">
-        <f>IFERROR(AGGREGATE(8,6,P9:AI9),"")</f>
+        <f t="array" ref="O9">IFERROR(STDEV(IF(ISNUMBER(P9:AI9),P9:AI9)),"")</f>
         <v>0</v>
       </c>
       <c r="P9">
@@ -45694,11 +45694,11 @@
         <v>0</v>
       </c>
       <c r="N10">
-        <f>IFERROR(AGGREGATE(1,6,P10:AI10),"")</f>
+        <f t="array" ref="N10">IFERROR(AVERAGE(IF(ISNUMBER(P10:AI10),P10:AI10)),"")</f>
         <v>0</v>
       </c>
       <c r="O10">
-        <f>IFERROR(AGGREGATE(8,6,P10:AI10),"")</f>
+        <f t="array" ref="O10">IFERROR(STDEV(IF(ISNUMBER(P10:AI10),P10:AI10)),"")</f>
         <v>0</v>
       </c>
       <c r="P10">
@@ -45832,11 +45832,11 @@
         <v>0</v>
       </c>
       <c r="N11">
-        <f>IFERROR(AGGREGATE(1,6,P11:AI11),"")</f>
+        <f t="array" ref="N11">IFERROR(AVERAGE(IF(ISNUMBER(P11:AI11),P11:AI11)),"")</f>
         <v>0</v>
       </c>
       <c r="O11">
-        <f>IFERROR(AGGREGATE(8,6,P11:AI11),"")</f>
+        <f t="array" ref="O11">IFERROR(STDEV(IF(ISNUMBER(P11:AI11),P11:AI11)),"")</f>
         <v>0</v>
       </c>
       <c r="P11">
@@ -45970,11 +45970,11 @@
         <v>0</v>
       </c>
       <c r="N12">
-        <f>IFERROR(AGGREGATE(1,6,P12:AI12),"")</f>
+        <f t="array" ref="N12">IFERROR(AVERAGE(IF(ISNUMBER(P12:AI12),P12:AI12)),"")</f>
         <v>0</v>
       </c>
       <c r="O12">
-        <f>IFERROR(AGGREGATE(8,6,P12:AI12),"")</f>
+        <f t="array" ref="O12">IFERROR(STDEV(IF(ISNUMBER(P12:AI12),P12:AI12)),"")</f>
         <v>0</v>
       </c>
       <c r="P12">
@@ -55525,11 +55525,11 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <f>IFERROR(AGGREGATE(1,6,P3:AI3),"")</f>
+        <f t="array" ref="N3">IFERROR(AVERAGE(IF(ISNUMBER(P3:AI3),P3:AI3)),"")</f>
         <v>0</v>
       </c>
       <c r="O3">
-        <f>IFERROR(AGGREGATE(8,6,P3:AI3),"")</f>
+        <f t="array" ref="O3">IFERROR(STDEV(IF(ISNUMBER(P3:AI3),P3:AI3)),"")</f>
         <v>0</v>
       </c>
       <c r="P3">
@@ -55663,11 +55663,11 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <f>IFERROR(AGGREGATE(1,6,P4:AI4),"")</f>
+        <f t="array" ref="N4">IFERROR(AVERAGE(IF(ISNUMBER(P4:AI4),P4:AI4)),"")</f>
         <v>0</v>
       </c>
       <c r="O4">
-        <f>IFERROR(AGGREGATE(8,6,P4:AI4),"")</f>
+        <f t="array" ref="O4">IFERROR(STDEV(IF(ISNUMBER(P4:AI4),P4:AI4)),"")</f>
         <v>0</v>
       </c>
       <c r="P4">
@@ -55801,11 +55801,11 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <f>IFERROR(AGGREGATE(1,6,P5:AI5),"")</f>
+        <f t="array" ref="N5">IFERROR(AVERAGE(IF(ISNUMBER(P5:AI5),P5:AI5)),"")</f>
         <v>0</v>
       </c>
       <c r="O5">
-        <f>IFERROR(AGGREGATE(8,6,P5:AI5),"")</f>
+        <f t="array" ref="O5">IFERROR(STDEV(IF(ISNUMBER(P5:AI5),P5:AI5)),"")</f>
         <v>0</v>
       </c>
       <c r="P5">
@@ -55939,11 +55939,11 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <f>IFERROR(AGGREGATE(1,6,P6:AI6),"")</f>
+        <f t="array" ref="N6">IFERROR(AVERAGE(IF(ISNUMBER(P6:AI6),P6:AI6)),"")</f>
         <v>0</v>
       </c>
       <c r="O6">
-        <f>IFERROR(AGGREGATE(8,6,P6:AI6),"")</f>
+        <f t="array" ref="O6">IFERROR(STDEV(IF(ISNUMBER(P6:AI6),P6:AI6)),"")</f>
         <v>0</v>
       </c>
       <c r="P6">
@@ -56077,11 +56077,11 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <f>IFERROR(AGGREGATE(1,6,P7:AI7),"")</f>
+        <f t="array" ref="N7">IFERROR(AVERAGE(IF(ISNUMBER(P7:AI7),P7:AI7)),"")</f>
         <v>0</v>
       </c>
       <c r="O7">
-        <f>IFERROR(AGGREGATE(8,6,P7:AI7),"")</f>
+        <f t="array" ref="O7">IFERROR(STDEV(IF(ISNUMBER(P7:AI7),P7:AI7)),"")</f>
         <v>0</v>
       </c>
       <c r="P7">
@@ -56215,11 +56215,11 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <f>IFERROR(AGGREGATE(1,6,P8:AI8),"")</f>
+        <f t="array" ref="N8">IFERROR(AVERAGE(IF(ISNUMBER(P8:AI8),P8:AI8)),"")</f>
         <v>0</v>
       </c>
       <c r="O8">
-        <f>IFERROR(AGGREGATE(8,6,P8:AI8),"")</f>
+        <f t="array" ref="O8">IFERROR(STDEV(IF(ISNUMBER(P8:AI8),P8:AI8)),"")</f>
         <v>0</v>
       </c>
       <c r="P8">
@@ -56353,11 +56353,11 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <f>IFERROR(AGGREGATE(1,6,P9:AI9),"")</f>
+        <f t="array" ref="N9">IFERROR(AVERAGE(IF(ISNUMBER(P9:AI9),P9:AI9)),"")</f>
         <v>0</v>
       </c>
       <c r="O9">
-        <f>IFERROR(AGGREGATE(8,6,P9:AI9),"")</f>
+        <f t="array" ref="O9">IFERROR(STDEV(IF(ISNUMBER(P9:AI9),P9:AI9)),"")</f>
         <v>0</v>
       </c>
       <c r="P9">
@@ -56491,11 +56491,11 @@
         <v>0</v>
       </c>
       <c r="N10">
-        <f>IFERROR(AGGREGATE(1,6,P10:AI10),"")</f>
+        <f t="array" ref="N10">IFERROR(AVERAGE(IF(ISNUMBER(P10:AI10),P10:AI10)),"")</f>
         <v>0</v>
       </c>
       <c r="O10">
-        <f>IFERROR(AGGREGATE(8,6,P10:AI10),"")</f>
+        <f t="array" ref="O10">IFERROR(STDEV(IF(ISNUMBER(P10:AI10),P10:AI10)),"")</f>
         <v>0</v>
       </c>
       <c r="P10">
@@ -56629,11 +56629,11 @@
         <v>0</v>
       </c>
       <c r="N11">
-        <f>IFERROR(AGGREGATE(1,6,P11:AI11),"")</f>
+        <f t="array" ref="N11">IFERROR(AVERAGE(IF(ISNUMBER(P11:AI11),P11:AI11)),"")</f>
         <v>0</v>
       </c>
       <c r="O11">
-        <f>IFERROR(AGGREGATE(8,6,P11:AI11),"")</f>
+        <f t="array" ref="O11">IFERROR(STDEV(IF(ISNUMBER(P11:AI11),P11:AI11)),"")</f>
         <v>0</v>
       </c>
       <c r="P11">
@@ -56767,11 +56767,11 @@
         <v>0</v>
       </c>
       <c r="N12">
-        <f>IFERROR(AGGREGATE(1,6,P12:AI12),"")</f>
+        <f t="array" ref="N12">IFERROR(AVERAGE(IF(ISNUMBER(P12:AI12),P12:AI12)),"")</f>
         <v>0</v>
       </c>
       <c r="O12">
-        <f>IFERROR(AGGREGATE(8,6,P12:AI12),"")</f>
+        <f t="array" ref="O12">IFERROR(STDEV(IF(ISNUMBER(P12:AI12),P12:AI12)),"")</f>
         <v>0</v>
       </c>
       <c r="P12">
@@ -64525,11 +64525,11 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <f>IFERROR(AGGREGATE(1,6,P3:AI3),"")</f>
+        <f t="array" ref="N3">IFERROR(AVERAGE(IF(ISNUMBER(P3:AI3),P3:AI3)),"")</f>
         <v>0</v>
       </c>
       <c r="O3">
-        <f>IFERROR(AGGREGATE(8,6,P3:AI3),"")</f>
+        <f t="array" ref="O3">IFERROR(STDEV(IF(ISNUMBER(P3:AI3),P3:AI3)),"")</f>
         <v>0</v>
       </c>
       <c r="P3">
@@ -64663,11 +64663,11 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <f>IFERROR(AGGREGATE(1,6,P4:AI4),"")</f>
+        <f t="array" ref="N4">IFERROR(AVERAGE(IF(ISNUMBER(P4:AI4),P4:AI4)),"")</f>
         <v>0</v>
       </c>
       <c r="O4">
-        <f>IFERROR(AGGREGATE(8,6,P4:AI4),"")</f>
+        <f t="array" ref="O4">IFERROR(STDEV(IF(ISNUMBER(P4:AI4),P4:AI4)),"")</f>
         <v>0</v>
       </c>
       <c r="P4">
@@ -64801,11 +64801,11 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <f>IFERROR(AGGREGATE(1,6,P5:AI5),"")</f>
+        <f t="array" ref="N5">IFERROR(AVERAGE(IF(ISNUMBER(P5:AI5),P5:AI5)),"")</f>
         <v>0</v>
       </c>
       <c r="O5">
-        <f>IFERROR(AGGREGATE(8,6,P5:AI5),"")</f>
+        <f t="array" ref="O5">IFERROR(STDEV(IF(ISNUMBER(P5:AI5),P5:AI5)),"")</f>
         <v>0</v>
       </c>
       <c r="P5">
@@ -64939,11 +64939,11 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <f>IFERROR(AGGREGATE(1,6,P6:AI6),"")</f>
+        <f t="array" ref="N6">IFERROR(AVERAGE(IF(ISNUMBER(P6:AI6),P6:AI6)),"")</f>
         <v>0</v>
       </c>
       <c r="O6">
-        <f>IFERROR(AGGREGATE(8,6,P6:AI6),"")</f>
+        <f t="array" ref="O6">IFERROR(STDEV(IF(ISNUMBER(P6:AI6),P6:AI6)),"")</f>
         <v>0</v>
       </c>
       <c r="P6">
@@ -65077,11 +65077,11 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <f>IFERROR(AGGREGATE(1,6,P7:AI7),"")</f>
+        <f t="array" ref="N7">IFERROR(AVERAGE(IF(ISNUMBER(P7:AI7),P7:AI7)),"")</f>
         <v>0</v>
       </c>
       <c r="O7">
-        <f>IFERROR(AGGREGATE(8,6,P7:AI7),"")</f>
+        <f t="array" ref="O7">IFERROR(STDEV(IF(ISNUMBER(P7:AI7),P7:AI7)),"")</f>
         <v>0</v>
       </c>
       <c r="P7">
@@ -65215,11 +65215,11 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <f>IFERROR(AGGREGATE(1,6,P8:AI8),"")</f>
+        <f t="array" ref="N8">IFERROR(AVERAGE(IF(ISNUMBER(P8:AI8),P8:AI8)),"")</f>
         <v>0</v>
       </c>
       <c r="O8">
-        <f>IFERROR(AGGREGATE(8,6,P8:AI8),"")</f>
+        <f t="array" ref="O8">IFERROR(STDEV(IF(ISNUMBER(P8:AI8),P8:AI8)),"")</f>
         <v>0</v>
       </c>
       <c r="P8">
@@ -65353,11 +65353,11 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <f>IFERROR(AGGREGATE(1,6,P9:AI9),"")</f>
+        <f t="array" ref="N9">IFERROR(AVERAGE(IF(ISNUMBER(P9:AI9),P9:AI9)),"")</f>
         <v>0</v>
       </c>
       <c r="O9">
-        <f>IFERROR(AGGREGATE(8,6,P9:AI9),"")</f>
+        <f t="array" ref="O9">IFERROR(STDEV(IF(ISNUMBER(P9:AI9),P9:AI9)),"")</f>
         <v>0</v>
       </c>
       <c r="P9">
@@ -65491,11 +65491,11 @@
         <v>0</v>
       </c>
       <c r="N10">
-        <f>IFERROR(AGGREGATE(1,6,P10:AI10),"")</f>
+        <f t="array" ref="N10">IFERROR(AVERAGE(IF(ISNUMBER(P10:AI10),P10:AI10)),"")</f>
         <v>0</v>
       </c>
       <c r="O10">
-        <f>IFERROR(AGGREGATE(8,6,P10:AI10),"")</f>
+        <f t="array" ref="O10">IFERROR(STDEV(IF(ISNUMBER(P10:AI10),P10:AI10)),"")</f>
         <v>0</v>
       </c>
       <c r="P10">
@@ -65629,11 +65629,11 @@
         <v>0</v>
       </c>
       <c r="N11">
-        <f>IFERROR(AGGREGATE(1,6,P11:AI11),"")</f>
+        <f t="array" ref="N11">IFERROR(AVERAGE(IF(ISNUMBER(P11:AI11),P11:AI11)),"")</f>
         <v>0</v>
       </c>
       <c r="O11">
-        <f>IFERROR(AGGREGATE(8,6,P11:AI11),"")</f>
+        <f t="array" ref="O11">IFERROR(STDEV(IF(ISNUMBER(P11:AI11),P11:AI11)),"")</f>
         <v>0</v>
       </c>
       <c r="P11">
@@ -65767,11 +65767,11 @@
         <v>0</v>
       </c>
       <c r="N12">
-        <f>IFERROR(AGGREGATE(1,6,P12:AI12),"")</f>
+        <f t="array" ref="N12">IFERROR(AVERAGE(IF(ISNUMBER(P12:AI12),P12:AI12)),"")</f>
         <v>0</v>
       </c>
       <c r="O12">
-        <f>IFERROR(AGGREGATE(8,6,P12:AI12),"")</f>
+        <f t="array" ref="O12">IFERROR(STDEV(IF(ISNUMBER(P12:AI12),P12:AI12)),"")</f>
         <v>0</v>
       </c>
       <c r="P12">
@@ -72437,11 +72437,11 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <f>IFERROR(AGGREGATE(1,6,P3:AI3),"")</f>
+        <f t="array" ref="N3">IFERROR(AVERAGE(IF(ISNUMBER(P3:AI3),P3:AI3)),"")</f>
         <v>0</v>
       </c>
       <c r="O3">
-        <f>IFERROR(AGGREGATE(8,6,P3:AI3),"")</f>
+        <f t="array" ref="O3">IFERROR(STDEV(IF(ISNUMBER(P3:AI3),P3:AI3)),"")</f>
         <v>0</v>
       </c>
       <c r="P3">
@@ -72575,11 +72575,11 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <f>IFERROR(AGGREGATE(1,6,P4:AI4),"")</f>
+        <f t="array" ref="N4">IFERROR(AVERAGE(IF(ISNUMBER(P4:AI4),P4:AI4)),"")</f>
         <v>0</v>
       </c>
       <c r="O4">
-        <f>IFERROR(AGGREGATE(8,6,P4:AI4),"")</f>
+        <f t="array" ref="O4">IFERROR(STDEV(IF(ISNUMBER(P4:AI4),P4:AI4)),"")</f>
         <v>0</v>
       </c>
       <c r="P4">
@@ -72713,11 +72713,11 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <f>IFERROR(AGGREGATE(1,6,P5:AI5),"")</f>
+        <f t="array" ref="N5">IFERROR(AVERAGE(IF(ISNUMBER(P5:AI5),P5:AI5)),"")</f>
         <v>0</v>
       </c>
       <c r="O5">
-        <f>IFERROR(AGGREGATE(8,6,P5:AI5),"")</f>
+        <f t="array" ref="O5">IFERROR(STDEV(IF(ISNUMBER(P5:AI5),P5:AI5)),"")</f>
         <v>0</v>
       </c>
       <c r="P5">
@@ -72851,11 +72851,11 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <f>IFERROR(AGGREGATE(1,6,P6:AI6),"")</f>
+        <f t="array" ref="N6">IFERROR(AVERAGE(IF(ISNUMBER(P6:AI6),P6:AI6)),"")</f>
         <v>0</v>
       </c>
       <c r="O6">
-        <f>IFERROR(AGGREGATE(8,6,P6:AI6),"")</f>
+        <f t="array" ref="O6">IFERROR(STDEV(IF(ISNUMBER(P6:AI6),P6:AI6)),"")</f>
         <v>0</v>
       </c>
       <c r="P6">
@@ -72989,11 +72989,11 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <f>IFERROR(AGGREGATE(1,6,P7:AI7),"")</f>
+        <f t="array" ref="N7">IFERROR(AVERAGE(IF(ISNUMBER(P7:AI7),P7:AI7)),"")</f>
         <v>0</v>
       </c>
       <c r="O7">
-        <f>IFERROR(AGGREGATE(8,6,P7:AI7),"")</f>
+        <f t="array" ref="O7">IFERROR(STDEV(IF(ISNUMBER(P7:AI7),P7:AI7)),"")</f>
         <v>0</v>
       </c>
       <c r="P7">
@@ -73127,11 +73127,11 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <f>IFERROR(AGGREGATE(1,6,P8:AI8),"")</f>
+        <f t="array" ref="N8">IFERROR(AVERAGE(IF(ISNUMBER(P8:AI8),P8:AI8)),"")</f>
         <v>0</v>
       </c>
       <c r="O8">
-        <f>IFERROR(AGGREGATE(8,6,P8:AI8),"")</f>
+        <f t="array" ref="O8">IFERROR(STDEV(IF(ISNUMBER(P8:AI8),P8:AI8)),"")</f>
         <v>0</v>
       </c>
       <c r="P8">
@@ -73265,11 +73265,11 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <f>IFERROR(AGGREGATE(1,6,P9:AI9),"")</f>
+        <f t="array" ref="N9">IFERROR(AVERAGE(IF(ISNUMBER(P9:AI9),P9:AI9)),"")</f>
         <v>0</v>
       </c>
       <c r="O9">
-        <f>IFERROR(AGGREGATE(8,6,P9:AI9),"")</f>
+        <f t="array" ref="O9">IFERROR(STDEV(IF(ISNUMBER(P9:AI9),P9:AI9)),"")</f>
         <v>0</v>
       </c>
       <c r="P9">
@@ -73403,11 +73403,11 @@
         <v>0</v>
       </c>
       <c r="N10">
-        <f>IFERROR(AGGREGATE(1,6,P10:AI10),"")</f>
+        <f t="array" ref="N10">IFERROR(AVERAGE(IF(ISNUMBER(P10:AI10),P10:AI10)),"")</f>
         <v>0</v>
       </c>
       <c r="O10">
-        <f>IFERROR(AGGREGATE(8,6,P10:AI10),"")</f>
+        <f t="array" ref="O10">IFERROR(STDEV(IF(ISNUMBER(P10:AI10),P10:AI10)),"")</f>
         <v>0</v>
       </c>
       <c r="P10">
@@ -73541,11 +73541,11 @@
         <v>0</v>
       </c>
       <c r="N11">
-        <f>IFERROR(AGGREGATE(1,6,P11:AI11),"")</f>
+        <f t="array" ref="N11">IFERROR(AVERAGE(IF(ISNUMBER(P11:AI11),P11:AI11)),"")</f>
         <v>0</v>
       </c>
       <c r="O11">
-        <f>IFERROR(AGGREGATE(8,6,P11:AI11),"")</f>
+        <f t="array" ref="O11">IFERROR(STDEV(IF(ISNUMBER(P11:AI11),P11:AI11)),"")</f>
         <v>0</v>
       </c>
       <c r="P11">
@@ -73679,11 +73679,11 @@
         <v>0</v>
       </c>
       <c r="N12">
-        <f>IFERROR(AGGREGATE(1,6,P12:AI12),"")</f>
+        <f t="array" ref="N12">IFERROR(AVERAGE(IF(ISNUMBER(P12:AI12),P12:AI12)),"")</f>
         <v>0</v>
       </c>
       <c r="O12">
-        <f>IFERROR(AGGREGATE(8,6,P12:AI12),"")</f>
+        <f t="array" ref="O12">IFERROR(STDEV(IF(ISNUMBER(P12:AI12),P12:AI12)),"")</f>
         <v>0</v>
       </c>
       <c r="P12">
@@ -79805,11 +79805,11 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <f>IFERROR(AGGREGATE(1,6,P3:AI3),"")</f>
+        <f t="array" ref="N3">IFERROR(AVERAGE(IF(ISNUMBER(P3:AI3),P3:AI3)),"")</f>
         <v>0</v>
       </c>
       <c r="O3">
-        <f>IFERROR(AGGREGATE(8,6,P3:AI3),"")</f>
+        <f t="array" ref="O3">IFERROR(STDEV(IF(ISNUMBER(P3:AI3),P3:AI3)),"")</f>
         <v>0</v>
       </c>
       <c r="P3">
@@ -79943,11 +79943,11 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <f>IFERROR(AGGREGATE(1,6,P4:AI4),"")</f>
+        <f t="array" ref="N4">IFERROR(AVERAGE(IF(ISNUMBER(P4:AI4),P4:AI4)),"")</f>
         <v>0</v>
       </c>
       <c r="O4">
-        <f>IFERROR(AGGREGATE(8,6,P4:AI4),"")</f>
+        <f t="array" ref="O4">IFERROR(STDEV(IF(ISNUMBER(P4:AI4),P4:AI4)),"")</f>
         <v>0</v>
       </c>
       <c r="P4">
@@ -80081,11 +80081,11 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <f>IFERROR(AGGREGATE(1,6,P5:AI5),"")</f>
+        <f t="array" ref="N5">IFERROR(AVERAGE(IF(ISNUMBER(P5:AI5),P5:AI5)),"")</f>
         <v>0</v>
       </c>
       <c r="O5">
-        <f>IFERROR(AGGREGATE(8,6,P5:AI5),"")</f>
+        <f t="array" ref="O5">IFERROR(STDEV(IF(ISNUMBER(P5:AI5),P5:AI5)),"")</f>
         <v>0</v>
       </c>
       <c r="P5">
@@ -80219,11 +80219,11 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <f>IFERROR(AGGREGATE(1,6,P6:AI6),"")</f>
+        <f t="array" ref="N6">IFERROR(AVERAGE(IF(ISNUMBER(P6:AI6),P6:AI6)),"")</f>
         <v>0</v>
       </c>
       <c r="O6">
-        <f>IFERROR(AGGREGATE(8,6,P6:AI6),"")</f>
+        <f t="array" ref="O6">IFERROR(STDEV(IF(ISNUMBER(P6:AI6),P6:AI6)),"")</f>
         <v>0</v>
       </c>
       <c r="P6">
@@ -80357,11 +80357,11 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <f>IFERROR(AGGREGATE(1,6,P7:AI7),"")</f>
+        <f t="array" ref="N7">IFERROR(AVERAGE(IF(ISNUMBER(P7:AI7),P7:AI7)),"")</f>
         <v>0</v>
       </c>
       <c r="O7">
-        <f>IFERROR(AGGREGATE(8,6,P7:AI7),"")</f>
+        <f t="array" ref="O7">IFERROR(STDEV(IF(ISNUMBER(P7:AI7),P7:AI7)),"")</f>
         <v>0</v>
       </c>
       <c r="P7">
@@ -80495,11 +80495,11 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <f>IFERROR(AGGREGATE(1,6,P8:AI8),"")</f>
+        <f t="array" ref="N8">IFERROR(AVERAGE(IF(ISNUMBER(P8:AI8),P8:AI8)),"")</f>
         <v>0</v>
       </c>
       <c r="O8">
-        <f>IFERROR(AGGREGATE(8,6,P8:AI8),"")</f>
+        <f t="array" ref="O8">IFERROR(STDEV(IF(ISNUMBER(P8:AI8),P8:AI8)),"")</f>
         <v>0</v>
       </c>
       <c r="P8">
@@ -80633,11 +80633,11 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <f>IFERROR(AGGREGATE(1,6,P9:AI9),"")</f>
+        <f t="array" ref="N9">IFERROR(AVERAGE(IF(ISNUMBER(P9:AI9),P9:AI9)),"")</f>
         <v>0</v>
       </c>
       <c r="O9">
-        <f>IFERROR(AGGREGATE(8,6,P9:AI9),"")</f>
+        <f t="array" ref="O9">IFERROR(STDEV(IF(ISNUMBER(P9:AI9),P9:AI9)),"")</f>
         <v>0</v>
       </c>
       <c r="P9">
@@ -80771,11 +80771,11 @@
         <v>0</v>
       </c>
       <c r="N10">
-        <f>IFERROR(AGGREGATE(1,6,P10:AI10),"")</f>
+        <f t="array" ref="N10">IFERROR(AVERAGE(IF(ISNUMBER(P10:AI10),P10:AI10)),"")</f>
         <v>0</v>
       </c>
       <c r="O10">
-        <f>IFERROR(AGGREGATE(8,6,P10:AI10),"")</f>
+        <f t="array" ref="O10">IFERROR(STDEV(IF(ISNUMBER(P10:AI10),P10:AI10)),"")</f>
         <v>0</v>
       </c>
       <c r="P10">
@@ -80909,11 +80909,11 @@
         <v>0</v>
       </c>
       <c r="N11">
-        <f>IFERROR(AGGREGATE(1,6,P11:AI11),"")</f>
+        <f t="array" ref="N11">IFERROR(AVERAGE(IF(ISNUMBER(P11:AI11),P11:AI11)),"")</f>
         <v>0</v>
       </c>
       <c r="O11">
-        <f>IFERROR(AGGREGATE(8,6,P11:AI11),"")</f>
+        <f t="array" ref="O11">IFERROR(STDEV(IF(ISNUMBER(P11:AI11),P11:AI11)),"")</f>
         <v>0</v>
       </c>
       <c r="P11">
@@ -81047,11 +81047,11 @@
         <v>0</v>
       </c>
       <c r="N12">
-        <f>IFERROR(AGGREGATE(1,6,P12:AI12),"")</f>
+        <f t="array" ref="N12">IFERROR(AVERAGE(IF(ISNUMBER(P12:AI12),P12:AI12)),"")</f>
         <v>0</v>
       </c>
       <c r="O12">
-        <f>IFERROR(AGGREGATE(8,6,P12:AI12),"")</f>
+        <f t="array" ref="O12">IFERROR(STDEV(IF(ISNUMBER(P12:AI12),P12:AI12)),"")</f>
         <v>0</v>
       </c>
       <c r="P12">
